--- a/copart_competitive_data.xlsx
+++ b/copart_competitive_data.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Vehicles Sold Annually" sheetId="9" r:id="rId9"/>
     <sheet name="Average Daily Inventory" sheetId="10" r:id="rId10"/>
     <sheet name="Towing &amp; Transporter Network" sheetId="11" r:id="rId11"/>
-    <sheet name="Title Processing (Insurance - S" sheetId="12" r:id="rId12"/>
+    <sheet name="Title Processing — All Channels" sheetId="12" r:id="rId12"/>
     <sheet name="Total Employees" sheetId="13" r:id="rId13"/>
     <sheet name="Glassdoor Employee Rating" sheetId="14" r:id="rId14"/>
     <sheet name="Years in Operation" sheetId="15" r:id="rId15"/>
@@ -27,7 +27,8 @@
     <sheet name="Monthly Social &amp; Web Mentions" sheetId="22" r:id="rId22"/>
     <sheet name="B2B Auction Mentions (Excl. Ret" sheetId="23" r:id="rId23"/>
     <sheet name="YouTube Channel Subscribers" sheetId="24" r:id="rId24"/>
-    <sheet name="Estimated Monthly SEM Spend" sheetId="25" r:id="rId25"/>
+    <sheet name="Monthly YouTube Mentions" sheetId="25" r:id="rId25"/>
+    <sheet name="Estimated Monthly SEM Spend" sheetId="26" r:id="rId26"/>
   </sheets>
 </workbook>
 </file>
@@ -421,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <cols>
     <col min="1" max="1" width="36.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -852,31 +853,31 @@
       <c r="C14">
         <v>10</v>
       </c>
-      <c r="D14" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="E14" t="str">
-        <v>N/A</v>
+      <c r="D14">
+        <v>4</v>
+      </c>
+      <c r="E14">
+        <v>0.5</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
-      <c r="G14" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H14" t="str">
-        <v>N/A</v>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>2</v>
       </c>
       <c r="I14" t="str">
         <v>N/A</v>
       </c>
       <c r="J14" t="str">
-        <v>Thousands of Contracted Providers</v>
+        <v>Thousands of Providers / Vehicles</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" t="str">
-        <v>Title Processing (Insurance / Salvage)</v>
+        <v>Title Processing — All Channels</v>
       </c>
       <c r="B15">
         <v>3.2</v>
@@ -884,20 +885,20 @@
       <c r="C15">
         <v>2.1</v>
       </c>
-      <c r="D15" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="E15" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="F15" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="G15" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H15" t="str">
-        <v>N/A</v>
+      <c r="D15">
+        <v>7</v>
+      </c>
+      <c r="E15">
+        <v>1.3</v>
+      </c>
+      <c r="F15">
+        <v>0.55</v>
+      </c>
+      <c r="G15">
+        <v>1.8</v>
+      </c>
+      <c r="H15">
+        <v>0.8</v>
       </c>
       <c r="I15" t="str">
         <v>N/A</v>
@@ -1292,33 +1293,65 @@
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" t="str">
+        <v>Monthly YouTube Mentions</v>
+      </c>
+      <c r="B28">
+        <v>8</v>
+      </c>
+      <c r="C28">
+        <v>4</v>
+      </c>
+      <c r="D28">
+        <v>6</v>
+      </c>
+      <c r="E28">
+        <v>1.5</v>
+      </c>
+      <c r="F28">
+        <v>2</v>
+      </c>
+      <c r="G28">
+        <v>95</v>
+      </c>
+      <c r="H28">
+        <v>120</v>
+      </c>
+      <c r="I28">
+        <v>18</v>
+      </c>
+      <c r="J28" t="str">
+        <v>Thousands / Month</v>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" t="str">
         <v>Estimated Monthly SEM Spend</v>
       </c>
-      <c r="B28">
+      <c r="B29">
         <v>1.1</v>
       </c>
-      <c r="C28">
+      <c r="C29">
         <v>0.6</v>
       </c>
-      <c r="D28">
+      <c r="D29">
         <v>0.75</v>
       </c>
-      <c r="E28">
+      <c r="E29">
         <v>0.35</v>
       </c>
-      <c r="F28">
+      <c r="F29">
         <v>0.45</v>
       </c>
-      <c r="G28">
+      <c r="G29">
         <v>11.5</v>
       </c>
-      <c r="H28">
+      <c r="H29">
         <v>15</v>
       </c>
-      <c r="I28">
+      <c r="I29">
         <v>5</v>
       </c>
-      <c r="J28" t="str">
+      <c r="J29" t="str">
         <v>USD Millions / Month</v>
       </c>
     </row>
@@ -1329,7 +1362,7 @@
     <mergeCell ref="A3:I3"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J29"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J30"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1931,7 +1964,7 @@
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" t="str">
-        <v>Unit: Thousands of Contracted Providers   |   Contracted tow operators &amp; transport providers, 2024. Digital-only &amp; retail platforms = N/A.</v>
+        <v>Unit: Thousands of Providers / Vehicles   |   Contracted tow operators, carrier partners &amp; owned delivery fleets, 2024. Copart/IAA = tow operators; Manheim via Cox Ready Logistics; Carvana = own delivery fleet; eBay Motors = N/A.</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -2021,7 +2054,7 @@
         <v>Company</v>
       </c>
       <c r="B5" t="str">
-        <v>Value (Thousands of Contracted Providers)</v>
+        <v>Value (Thousands of Providers / Vehicles)</v>
       </c>
       <c r="C5" t="str">
         <v>Notes</v>
@@ -2053,7 +2086,7 @@
         <v>20</v>
       </c>
       <c r="C6" t="str">
-        <v>20 Thousands of Contracted Providers</v>
+        <v>20 Thousands of Providers / Vehicles</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -2082,7 +2115,7 @@
         <v>10</v>
       </c>
       <c r="C7" t="str">
-        <v>10 Thousands of Contracted Providers</v>
+        <v>10 Thousands of Providers / Vehicles</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -2107,11 +2140,11 @@
       <c r="A8" t="str">
         <v>Manheim</v>
       </c>
-      <c r="B8" t="str">
-        <v>N/A</v>
+      <c r="B8">
+        <v>4</v>
       </c>
       <c r="C8" t="str">
-        <v>Not applicable / not publicly reported</v>
+        <v>4 Thousands of Providers / Vehicles</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -2136,11 +2169,11 @@
       <c r="A9" t="str">
         <v>OpenLane</v>
       </c>
-      <c r="B9" t="str">
-        <v>N/A</v>
+      <c r="B9">
+        <v>0.5</v>
       </c>
       <c r="C9" t="str">
-        <v>Not applicable / not publicly reported</v>
+        <v>0.5 Thousands of Providers / Vehicles</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -2169,7 +2202,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="str">
-        <v>1 Thousands of Contracted Providers</v>
+        <v>1 Thousands of Providers / Vehicles</v>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -2194,11 +2227,11 @@
       <c r="A11" t="str">
         <v>CarMax</v>
       </c>
-      <c r="B11" t="str">
-        <v>N/A</v>
+      <c r="B11">
+        <v>1</v>
       </c>
       <c r="C11" t="str">
-        <v>Not applicable / not publicly reported</v>
+        <v>1 Thousands of Providers / Vehicles</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -2223,11 +2256,11 @@
       <c r="A12" t="str">
         <v>Carvana</v>
       </c>
-      <c r="B12" t="str">
-        <v>N/A</v>
+      <c r="B12">
+        <v>2</v>
       </c>
       <c r="C12" t="str">
-        <v>Not applicable / not publicly reported</v>
+        <v>2 Thousands of Providers / Vehicles</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -2374,20 +2407,20 @@
       <c r="C17">
         <v>10</v>
       </c>
-      <c r="D17" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="E17" t="str">
-        <v>N/A</v>
+      <c r="D17">
+        <v>4</v>
+      </c>
+      <c r="E17">
+        <v>0.5</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
-      <c r="G17" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H17" t="str">
-        <v>N/A</v>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>2</v>
       </c>
       <c r="I17" t="str">
         <v>N/A</v>
@@ -2398,28 +2431,28 @@
         <v>Unit</v>
       </c>
       <c r="B18" t="str">
-        <v>Thousands of Contracted Providers</v>
+        <v>Thousands of Providers / Vehicles</v>
       </c>
       <c r="C18" t="str">
-        <v>Thousands of Contracted Providers</v>
+        <v>Thousands of Providers / Vehicles</v>
       </c>
       <c r="D18" t="str">
-        <v>Thousands of Contracted Providers</v>
+        <v>Thousands of Providers / Vehicles</v>
       </c>
       <c r="E18" t="str">
-        <v>Thousands of Contracted Providers</v>
+        <v>Thousands of Providers / Vehicles</v>
       </c>
       <c r="F18" t="str">
-        <v>Thousands of Contracted Providers</v>
+        <v>Thousands of Providers / Vehicles</v>
       </c>
       <c r="G18" t="str">
-        <v>Thousands of Contracted Providers</v>
+        <v>Thousands of Providers / Vehicles</v>
       </c>
       <c r="H18" t="str">
-        <v>Thousands of Contracted Providers</v>
+        <v>Thousands of Providers / Vehicles</v>
       </c>
       <c r="I18" t="str">
-        <v>Thousands of Contracted Providers</v>
+        <v>Thousands of Providers / Vehicles</v>
       </c>
     </row>
   </sheetData>
@@ -2453,7 +2486,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" t="str">
-        <v>Title Processing (Insurance / Salvage)</v>
+        <v>Title Processing — All Channels</v>
       </c>
       <c r="B1" t="str">
         <v/>
@@ -2482,7 +2515,7 @@
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" t="str">
-        <v>Unit: Millions of Titles / Year   |   Annual salvage &amp; insurance-seller titles processed, FY2024. Only Copart &amp; IAA operate at scale for this.</v>
+        <v>Unit: Millions of Titles / Year   |   Annual titles processed or facilitated, FY2024. Copart &amp; IAA = insurance/salvage. Manheim/OpenLane/ACV = wholesale dealer facilitation. CarMax &amp; Carvana = retail title transfers. eBay Motors = N/A.</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -2658,11 +2691,11 @@
       <c r="A8" t="str">
         <v>Manheim</v>
       </c>
-      <c r="B8" t="str">
-        <v>N/A</v>
+      <c r="B8">
+        <v>7</v>
       </c>
       <c r="C8" t="str">
-        <v>Not applicable / not publicly reported</v>
+        <v>7 Millions of Titles / Year</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -2687,11 +2720,11 @@
       <c r="A9" t="str">
         <v>OpenLane</v>
       </c>
-      <c r="B9" t="str">
-        <v>N/A</v>
+      <c r="B9">
+        <v>1.3</v>
       </c>
       <c r="C9" t="str">
-        <v>Not applicable / not publicly reported</v>
+        <v>1.3 Millions of Titles / Year</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -2716,11 +2749,11 @@
       <c r="A10" t="str">
         <v>ACV</v>
       </c>
-      <c r="B10" t="str">
-        <v>N/A</v>
+      <c r="B10">
+        <v>0.55</v>
       </c>
       <c r="C10" t="str">
-        <v>Not applicable / not publicly reported</v>
+        <v>0.55 Millions of Titles / Year</v>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -2745,11 +2778,11 @@
       <c r="A11" t="str">
         <v>CarMax</v>
       </c>
-      <c r="B11" t="str">
-        <v>N/A</v>
+      <c r="B11">
+        <v>1.8</v>
       </c>
       <c r="C11" t="str">
-        <v>Not applicable / not publicly reported</v>
+        <v>1.8 Millions of Titles / Year</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -2774,11 +2807,11 @@
       <c r="A12" t="str">
         <v>Carvana</v>
       </c>
-      <c r="B12" t="str">
-        <v>N/A</v>
+      <c r="B12">
+        <v>0.8</v>
       </c>
       <c r="C12" t="str">
-        <v>Not applicable / not publicly reported</v>
+        <v>0.8 Millions of Titles / Year</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -2917,7 +2950,7 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" t="str">
-        <v>Title Processing (Insurance / Salvage)</v>
+        <v>Title Processing — All Channels</v>
       </c>
       <c r="B17">
         <v>3.2</v>
@@ -2925,20 +2958,20 @@
       <c r="C17">
         <v>2.1</v>
       </c>
-      <c r="D17" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="E17" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="F17" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="G17" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H17" t="str">
-        <v>N/A</v>
+      <c r="D17">
+        <v>7</v>
+      </c>
+      <c r="E17">
+        <v>1.3</v>
+      </c>
+      <c r="F17">
+        <v>0.55</v>
+      </c>
+      <c r="G17">
+        <v>1.8</v>
+      </c>
+      <c r="H17">
+        <v>0.8</v>
       </c>
       <c r="I17" t="str">
         <v>N/A</v>
@@ -10167,6 +10200,557 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" t="str">
+        <v>Monthly YouTube Mentions</v>
+      </c>
+      <c r="B1" t="str">
+        <v/>
+      </c>
+      <c r="C1" t="str">
+        <v/>
+      </c>
+      <c r="D1" t="str">
+        <v/>
+      </c>
+      <c r="E1" t="str">
+        <v/>
+      </c>
+      <c r="F1" t="str">
+        <v/>
+      </c>
+      <c r="G1" t="str">
+        <v/>
+      </c>
+      <c r="H1" t="str">
+        <v/>
+      </c>
+      <c r="I1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" t="str">
+        <v>Unit: Thousands / Month   |   Est. monthly brand video mentions on YouTube (dedicated videos, reviews, creator references), 2024.</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1">
+      <c r="A3" t="str">
+        <v/>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" t="str">
+        <v>VERTICAL LAYOUT</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" t="str">
+        <v>Company</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Value (Thousands / Month)</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Notes</v>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" t="str">
+        <v>Copart</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6" t="str">
+        <v>8 Thousands / Month</v>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" t="str">
+        <v>IAA</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7" t="str">
+        <v>4 Thousands / Month</v>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" t="str">
+        <v>Manheim</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8" t="str">
+        <v>6 Thousands / Month</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" t="str">
+        <v>OpenLane</v>
+      </c>
+      <c r="B9">
+        <v>1.5</v>
+      </c>
+      <c r="C9" t="str">
+        <v>1.5 Thousands / Month</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" t="str">
+        <v>ACV</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10" t="str">
+        <v>2 Thousands / Month</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" t="str">
+        <v>CarMax</v>
+      </c>
+      <c r="B11">
+        <v>95</v>
+      </c>
+      <c r="C11" t="str">
+        <v>95 Thousands / Month</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" t="str">
+        <v>Carvana</v>
+      </c>
+      <c r="B12">
+        <v>120</v>
+      </c>
+      <c r="C12" t="str">
+        <v>120 Thousands / Month</v>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" t="str">
+        <v>eBay Motors</v>
+      </c>
+      <c r="B13">
+        <v>18</v>
+      </c>
+      <c r="C13" t="str">
+        <v>18 Thousands / Month</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="8" customHeight="1">
+      <c r="A14" t="str">
+        <v/>
+      </c>
+      <c r="B14" t="str">
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" t="str">
+        <v>HORIZONTAL LAYOUT</v>
+      </c>
+      <c r="B15" t="str">
+        <v/>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" t="str">
+        <v>Metric</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Copart</v>
+      </c>
+      <c r="C16" t="str">
+        <v>IAA</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Manheim</v>
+      </c>
+      <c r="E16" t="str">
+        <v>OpenLane</v>
+      </c>
+      <c r="F16" t="str">
+        <v>ACV</v>
+      </c>
+      <c r="G16" t="str">
+        <v>CarMax</v>
+      </c>
+      <c r="H16" t="str">
+        <v>Carvana</v>
+      </c>
+      <c r="I16" t="str">
+        <v>eBay Motors</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" t="str">
+        <v>Monthly YouTube Mentions</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>4</v>
+      </c>
+      <c r="D17">
+        <v>6</v>
+      </c>
+      <c r="E17">
+        <v>1.5</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17">
+        <v>95</v>
+      </c>
+      <c r="H17">
+        <v>120</v>
+      </c>
+      <c r="I17">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Thousands / Month</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Thousands / Month</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Thousands / Month</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Thousands / Month</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Thousands / Month</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Thousands / Month</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Thousands / Month</v>
+      </c>
+      <c r="I18" t="str">
+        <v>Thousands / Month</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="A15:I15"/>
+  </mergeCells>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I18"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I18"/>
+  <cols>
+    <col min="1" max="1" width="28.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="42.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" t="str">
         <v>Estimated Monthly SEM Spend</v>
       </c>
       <c r="B1" t="str">

--- a/copart_competitive_data.xlsx
+++ b/copart_competitive_data.xlsx
@@ -4,31 +4,32 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
-    <sheet name="Annual Revenue" sheetId="2" r:id="rId2"/>
-    <sheet name="Market Capitalization" sheetId="3" r:id="rId3"/>
-    <sheet name="Capital Expenditure" sheetId="4" r:id="rId4"/>
-    <sheet name="Physical Locations" sheetId="5" r:id="rId5"/>
-    <sheet name="Land Footprint" sheetId="6" r:id="rId6"/>
-    <sheet name="Countries of Operation" sheetId="7" r:id="rId7"/>
-    <sheet name="Vehicles Auctioned - Available" sheetId="8" r:id="rId8"/>
-    <sheet name="Vehicles Sold Annually" sheetId="9" r:id="rId9"/>
-    <sheet name="Average Daily Inventory" sheetId="10" r:id="rId10"/>
-    <sheet name="Towing &amp; Transporter Network" sheetId="11" r:id="rId11"/>
-    <sheet name="Title Processing — All Channels" sheetId="12" r:id="rId12"/>
-    <sheet name="Total Employees" sheetId="13" r:id="rId13"/>
-    <sheet name="Glassdoor Employee Rating" sheetId="14" r:id="rId14"/>
-    <sheet name="Years in Operation" sheetId="15" r:id="rId15"/>
-    <sheet name="Main App Rating (iOS)" sheetId="16" r:id="rId16"/>
-    <sheet name="Main App Downloads" sheetId="17" r:id="rId17"/>
-    <sheet name="Driver App Rating (iOS)" sheetId="18" r:id="rId18"/>
-    <sheet name="Driver App Downloads" sheetId="19" r:id="rId19"/>
-    <sheet name="Registered Global Buyers" sheetId="20" r:id="rId20"/>
-    <sheet name="Buyer Countries" sheetId="21" r:id="rId21"/>
-    <sheet name="Monthly Social &amp; Web Mentions" sheetId="22" r:id="rId22"/>
-    <sheet name="B2B Auction Mentions (Excl. Ret" sheetId="23" r:id="rId23"/>
-    <sheet name="YouTube Channel Subscribers" sheetId="24" r:id="rId24"/>
-    <sheet name="Monthly YouTube Mentions" sheetId="25" r:id="rId25"/>
-    <sheet name="Estimated Monthly SEM Spend" sheetId="26" r:id="rId26"/>
+    <sheet name="Sources" sheetId="2" r:id="rId2"/>
+    <sheet name="Annual Revenue" sheetId="3" r:id="rId3"/>
+    <sheet name="Market Capitalization" sheetId="4" r:id="rId4"/>
+    <sheet name="Capital Expenditure" sheetId="5" r:id="rId5"/>
+    <sheet name="Physical Locations" sheetId="6" r:id="rId6"/>
+    <sheet name="Land Footprint" sheetId="7" r:id="rId7"/>
+    <sheet name="Countries of Operation" sheetId="8" r:id="rId8"/>
+    <sheet name="Vehicles Auctioned - Available" sheetId="9" r:id="rId9"/>
+    <sheet name="Vehicles Sold Annually" sheetId="10" r:id="rId10"/>
+    <sheet name="Average Daily Inventory" sheetId="11" r:id="rId11"/>
+    <sheet name="Towing &amp; Transporter Network" sheetId="12" r:id="rId12"/>
+    <sheet name="Title Processing — All Channels" sheetId="13" r:id="rId13"/>
+    <sheet name="Total Employees" sheetId="14" r:id="rId14"/>
+    <sheet name="Glassdoor Employee Rating" sheetId="15" r:id="rId15"/>
+    <sheet name="Years in Operation" sheetId="16" r:id="rId16"/>
+    <sheet name="Main App Rating (iOS)" sheetId="17" r:id="rId17"/>
+    <sheet name="Main App Downloads" sheetId="18" r:id="rId18"/>
+    <sheet name="Driver App Rating (iOS)" sheetId="19" r:id="rId19"/>
+    <sheet name="Driver App Downloads" sheetId="20" r:id="rId20"/>
+    <sheet name="Registered Global Buyers" sheetId="21" r:id="rId21"/>
+    <sheet name="Buyer Countries" sheetId="22" r:id="rId22"/>
+    <sheet name="Monthly Social &amp; Web Mentions" sheetId="23" r:id="rId23"/>
+    <sheet name="B2B Auction Mentions (Excl. Ret" sheetId="24" r:id="rId24"/>
+    <sheet name="YouTube Channel Subscribers" sheetId="25" r:id="rId25"/>
+    <sheet name="Monthly YouTube Mentions" sheetId="26" r:id="rId26"/>
+    <sheet name="Estimated Monthly SEM Spend" sheetId="27" r:id="rId27"/>
   </sheets>
 </workbook>
 </file>
@@ -1384,7 +1385,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" t="str">
-        <v>Average Daily Inventory</v>
+        <v>Vehicles Sold Annually</v>
       </c>
       <c r="B1" t="str">
         <v/>
@@ -1413,7 +1414,7 @@
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" t="str">
-        <v>Unit: Thousands of Vehicles   |   Vehicles available for bidding or purchase on any given day, 2024. eBay figure = vehicles only.</v>
+        <v>Unit: Millions / Year   |   Vehicles actually sold at auction / retail, FY2024. Reflects sell-through rate.</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -1503,7 +1504,7 @@
         <v>Company</v>
       </c>
       <c r="B5" t="str">
-        <v>Value (Thousands of Vehicles)</v>
+        <v>Value (Millions / Year)</v>
       </c>
       <c r="C5" t="str">
         <v>Notes</v>
@@ -1532,10 +1533,10 @@
         <v>Copart</v>
       </c>
       <c r="B6">
-        <v>180</v>
+        <v>3.5</v>
       </c>
       <c r="C6" t="str">
-        <v>180 Thousands of Vehicles</v>
+        <v>3.5 Millions / Year</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -1561,10 +1562,10 @@
         <v>IAA</v>
       </c>
       <c r="B7">
-        <v>125</v>
+        <v>2.2</v>
       </c>
       <c r="C7" t="str">
-        <v>125 Thousands of Vehicles</v>
+        <v>2.2 Millions / Year</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -1590,10 +1591,10 @@
         <v>Manheim</v>
       </c>
       <c r="B8">
-        <v>85</v>
+        <v>8.5</v>
       </c>
       <c r="C8" t="str">
-        <v>85 Thousands of Vehicles</v>
+        <v>8.5 Millions / Year</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -1619,10 +1620,10 @@
         <v>OpenLane</v>
       </c>
       <c r="B9">
-        <v>55</v>
+        <v>1.3</v>
       </c>
       <c r="C9" t="str">
-        <v>55 Thousands of Vehicles</v>
+        <v>1.3 Millions / Year</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -1648,10 +1649,10 @@
         <v>ACV</v>
       </c>
       <c r="B10">
-        <v>18</v>
+        <v>0.55</v>
       </c>
       <c r="C10" t="str">
-        <v>18 Thousands of Vehicles</v>
+        <v>0.55 Millions / Year</v>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -1677,10 +1678,10 @@
         <v>CarMax</v>
       </c>
       <c r="B11">
-        <v>55</v>
+        <v>0.9</v>
       </c>
       <c r="C11" t="str">
-        <v>55 Thousands of Vehicles</v>
+        <v>0.9 Millions / Year</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -1706,10 +1707,10 @@
         <v>Carvana</v>
       </c>
       <c r="B12">
-        <v>40</v>
+        <v>0.42</v>
       </c>
       <c r="C12" t="str">
-        <v>40 Thousands of Vehicles</v>
+        <v>0.42 Millions / Year</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -1735,10 +1736,10 @@
         <v>eBay Motors</v>
       </c>
       <c r="B13">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="C13" t="str">
-        <v>35 Thousands of Vehicles</v>
+        <v>2 Millions / Year</v>
       </c>
       <c r="D13" t="str">
         <v/>
@@ -1848,31 +1849,31 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" t="str">
-        <v>Average Daily Inventory</v>
+        <v>Vehicles Sold Annually</v>
       </c>
       <c r="B17">
-        <v>180</v>
+        <v>3.5</v>
       </c>
       <c r="C17">
-        <v>125</v>
+        <v>2.2</v>
       </c>
       <c r="D17">
-        <v>85</v>
+        <v>8.5</v>
       </c>
       <c r="E17">
-        <v>55</v>
+        <v>1.3</v>
       </c>
       <c r="F17">
-        <v>18</v>
+        <v>0.55</v>
       </c>
       <c r="G17">
-        <v>55</v>
+        <v>0.9</v>
       </c>
       <c r="H17">
-        <v>40</v>
+        <v>0.42</v>
       </c>
       <c r="I17">
-        <v>35</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -1880,28 +1881,28 @@
         <v>Unit</v>
       </c>
       <c r="B18" t="str">
-        <v>Thousands of Vehicles</v>
+        <v>Millions / Year</v>
       </c>
       <c r="C18" t="str">
-        <v>Thousands of Vehicles</v>
+        <v>Millions / Year</v>
       </c>
       <c r="D18" t="str">
-        <v>Thousands of Vehicles</v>
+        <v>Millions / Year</v>
       </c>
       <c r="E18" t="str">
-        <v>Thousands of Vehicles</v>
+        <v>Millions / Year</v>
       </c>
       <c r="F18" t="str">
-        <v>Thousands of Vehicles</v>
+        <v>Millions / Year</v>
       </c>
       <c r="G18" t="str">
-        <v>Thousands of Vehicles</v>
+        <v>Millions / Year</v>
       </c>
       <c r="H18" t="str">
-        <v>Thousands of Vehicles</v>
+        <v>Millions / Year</v>
       </c>
       <c r="I18" t="str">
-        <v>Thousands of Vehicles</v>
+        <v>Millions / Year</v>
       </c>
     </row>
   </sheetData>
@@ -1935,7 +1936,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" t="str">
-        <v>Towing &amp; Transporter Network</v>
+        <v>Average Daily Inventory</v>
       </c>
       <c r="B1" t="str">
         <v/>
@@ -1964,7 +1965,7 @@
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" t="str">
-        <v>Unit: Thousands of Providers / Vehicles   |   Contracted tow operators, carrier partners &amp; owned delivery fleets, 2024. Copart/IAA = tow operators; Manheim via Cox Ready Logistics; Carvana = own delivery fleet; eBay Motors = N/A.</v>
+        <v>Unit: Thousands of Vehicles   |   Vehicles available for bidding or purchase on any given day, 2024. eBay figure = vehicles only.</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -2054,7 +2055,7 @@
         <v>Company</v>
       </c>
       <c r="B5" t="str">
-        <v>Value (Thousands of Providers / Vehicles)</v>
+        <v>Value (Thousands of Vehicles)</v>
       </c>
       <c r="C5" t="str">
         <v>Notes</v>
@@ -2083,10 +2084,10 @@
         <v>Copart</v>
       </c>
       <c r="B6">
-        <v>20</v>
+        <v>180</v>
       </c>
       <c r="C6" t="str">
-        <v>20 Thousands of Providers / Vehicles</v>
+        <v>180 Thousands of Vehicles</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -2112,10 +2113,10 @@
         <v>IAA</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>125</v>
       </c>
       <c r="C7" t="str">
-        <v>10 Thousands of Providers / Vehicles</v>
+        <v>125 Thousands of Vehicles</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -2141,10 +2142,10 @@
         <v>Manheim</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>85</v>
       </c>
       <c r="C8" t="str">
-        <v>4 Thousands of Providers / Vehicles</v>
+        <v>85 Thousands of Vehicles</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -2170,10 +2171,10 @@
         <v>OpenLane</v>
       </c>
       <c r="B9">
-        <v>0.5</v>
+        <v>55</v>
       </c>
       <c r="C9" t="str">
-        <v>0.5 Thousands of Providers / Vehicles</v>
+        <v>55 Thousands of Vehicles</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -2199,10 +2200,10 @@
         <v>ACV</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C10" t="str">
-        <v>1 Thousands of Providers / Vehicles</v>
+        <v>18 Thousands of Vehicles</v>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -2228,10 +2229,10 @@
         <v>CarMax</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="C11" t="str">
-        <v>1 Thousands of Providers / Vehicles</v>
+        <v>55 Thousands of Vehicles</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -2257,10 +2258,10 @@
         <v>Carvana</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C12" t="str">
-        <v>2 Thousands of Providers / Vehicles</v>
+        <v>40 Thousands of Vehicles</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -2285,11 +2286,11 @@
       <c r="A13" t="str">
         <v>eBay Motors</v>
       </c>
-      <c r="B13" t="str">
-        <v>N/A</v>
+      <c r="B13">
+        <v>35</v>
       </c>
       <c r="C13" t="str">
-        <v>Not applicable / not publicly reported</v>
+        <v>35 Thousands of Vehicles</v>
       </c>
       <c r="D13" t="str">
         <v/>
@@ -2399,31 +2400,31 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" t="str">
-        <v>Towing &amp; Transporter Network</v>
+        <v>Average Daily Inventory</v>
       </c>
       <c r="B17">
-        <v>20</v>
+        <v>180</v>
       </c>
       <c r="C17">
-        <v>10</v>
+        <v>125</v>
       </c>
       <c r="D17">
-        <v>4</v>
+        <v>85</v>
       </c>
       <c r="E17">
-        <v>0.5</v>
+        <v>55</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="H17">
-        <v>2</v>
-      </c>
-      <c r="I17" t="str">
-        <v>N/A</v>
+        <v>40</v>
+      </c>
+      <c r="I17">
+        <v>35</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -2431,28 +2432,28 @@
         <v>Unit</v>
       </c>
       <c r="B18" t="str">
-        <v>Thousands of Providers / Vehicles</v>
+        <v>Thousands of Vehicles</v>
       </c>
       <c r="C18" t="str">
-        <v>Thousands of Providers / Vehicles</v>
+        <v>Thousands of Vehicles</v>
       </c>
       <c r="D18" t="str">
-        <v>Thousands of Providers / Vehicles</v>
+        <v>Thousands of Vehicles</v>
       </c>
       <c r="E18" t="str">
-        <v>Thousands of Providers / Vehicles</v>
+        <v>Thousands of Vehicles</v>
       </c>
       <c r="F18" t="str">
-        <v>Thousands of Providers / Vehicles</v>
+        <v>Thousands of Vehicles</v>
       </c>
       <c r="G18" t="str">
-        <v>Thousands of Providers / Vehicles</v>
+        <v>Thousands of Vehicles</v>
       </c>
       <c r="H18" t="str">
-        <v>Thousands of Providers / Vehicles</v>
+        <v>Thousands of Vehicles</v>
       </c>
       <c r="I18" t="str">
-        <v>Thousands of Providers / Vehicles</v>
+        <v>Thousands of Vehicles</v>
       </c>
     </row>
   </sheetData>
@@ -2486,7 +2487,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" t="str">
-        <v>Title Processing — All Channels</v>
+        <v>Towing &amp; Transporter Network</v>
       </c>
       <c r="B1" t="str">
         <v/>
@@ -2515,7 +2516,7 @@
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" t="str">
-        <v>Unit: Millions of Titles / Year   |   Annual titles processed or facilitated, FY2024. Copart &amp; IAA = insurance/salvage. Manheim/OpenLane/ACV = wholesale dealer facilitation. CarMax &amp; Carvana = retail title transfers. eBay Motors = N/A.</v>
+        <v>Unit: Thousands of Providers / Vehicles   |   Contracted tow operators, carrier partners &amp; owned delivery fleets, 2024. Copart/IAA = tow operators; Manheim via Cox Ready Logistics; Carvana = own delivery fleet; eBay Motors = N/A.</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -2605,7 +2606,7 @@
         <v>Company</v>
       </c>
       <c r="B5" t="str">
-        <v>Value (Millions of Titles / Year)</v>
+        <v>Value (Thousands of Providers / Vehicles)</v>
       </c>
       <c r="C5" t="str">
         <v>Notes</v>
@@ -2634,10 +2635,10 @@
         <v>Copart</v>
       </c>
       <c r="B6">
-        <v>3.2</v>
+        <v>20</v>
       </c>
       <c r="C6" t="str">
-        <v>3.2 Millions of Titles / Year</v>
+        <v>20 Thousands of Providers / Vehicles</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -2663,10 +2664,10 @@
         <v>IAA</v>
       </c>
       <c r="B7">
-        <v>2.1</v>
+        <v>10</v>
       </c>
       <c r="C7" t="str">
-        <v>2.1 Millions of Titles / Year</v>
+        <v>10 Thousands of Providers / Vehicles</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -2692,10 +2693,10 @@
         <v>Manheim</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C8" t="str">
-        <v>7 Millions of Titles / Year</v>
+        <v>4 Thousands of Providers / Vehicles</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -2721,10 +2722,10 @@
         <v>OpenLane</v>
       </c>
       <c r="B9">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="C9" t="str">
-        <v>1.3 Millions of Titles / Year</v>
+        <v>0.5 Thousands of Providers / Vehicles</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -2750,10 +2751,10 @@
         <v>ACV</v>
       </c>
       <c r="B10">
-        <v>0.55</v>
+        <v>1</v>
       </c>
       <c r="C10" t="str">
-        <v>0.55 Millions of Titles / Year</v>
+        <v>1 Thousands of Providers / Vehicles</v>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -2779,10 +2780,10 @@
         <v>CarMax</v>
       </c>
       <c r="B11">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="C11" t="str">
-        <v>1.8 Millions of Titles / Year</v>
+        <v>1 Thousands of Providers / Vehicles</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -2808,10 +2809,10 @@
         <v>Carvana</v>
       </c>
       <c r="B12">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="C12" t="str">
-        <v>0.8 Millions of Titles / Year</v>
+        <v>2 Thousands of Providers / Vehicles</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -2950,28 +2951,28 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" t="str">
-        <v>Title Processing — All Channels</v>
+        <v>Towing &amp; Transporter Network</v>
       </c>
       <c r="B17">
-        <v>3.2</v>
+        <v>20</v>
       </c>
       <c r="C17">
-        <v>2.1</v>
+        <v>10</v>
       </c>
       <c r="D17">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E17">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="F17">
-        <v>0.55</v>
+        <v>1</v>
       </c>
       <c r="G17">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="I17" t="str">
         <v>N/A</v>
@@ -2982,28 +2983,28 @@
         <v>Unit</v>
       </c>
       <c r="B18" t="str">
-        <v>Millions of Titles / Year</v>
+        <v>Thousands of Providers / Vehicles</v>
       </c>
       <c r="C18" t="str">
-        <v>Millions of Titles / Year</v>
+        <v>Thousands of Providers / Vehicles</v>
       </c>
       <c r="D18" t="str">
-        <v>Millions of Titles / Year</v>
+        <v>Thousands of Providers / Vehicles</v>
       </c>
       <c r="E18" t="str">
-        <v>Millions of Titles / Year</v>
+        <v>Thousands of Providers / Vehicles</v>
       </c>
       <c r="F18" t="str">
-        <v>Millions of Titles / Year</v>
+        <v>Thousands of Providers / Vehicles</v>
       </c>
       <c r="G18" t="str">
-        <v>Millions of Titles / Year</v>
+        <v>Thousands of Providers / Vehicles</v>
       </c>
       <c r="H18" t="str">
-        <v>Millions of Titles / Year</v>
+        <v>Thousands of Providers / Vehicles</v>
       </c>
       <c r="I18" t="str">
-        <v>Millions of Titles / Year</v>
+        <v>Thousands of Providers / Vehicles</v>
       </c>
     </row>
   </sheetData>
@@ -3037,7 +3038,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" t="str">
-        <v>Total Employees</v>
+        <v>Title Processing — All Channels</v>
       </c>
       <c r="B1" t="str">
         <v/>
@@ -3066,7 +3067,7 @@
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" t="str">
-        <v>Unit: Thousands (FTE)   |   Full-time equivalent headcount, 2024. eBay Motors employees not separately reportable.</v>
+        <v>Unit: Millions of Titles / Year   |   Annual titles processed or facilitated, FY2024. Copart &amp; IAA = insurance/salvage. Manheim/OpenLane/ACV = wholesale dealer facilitation. CarMax &amp; Carvana = retail title transfers. eBay Motors = N/A.</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -3156,7 +3157,7 @@
         <v>Company</v>
       </c>
       <c r="B5" t="str">
-        <v>Value (Thousands (FTE))</v>
+        <v>Value (Millions of Titles / Year)</v>
       </c>
       <c r="C5" t="str">
         <v>Notes</v>
@@ -3185,10 +3186,10 @@
         <v>Copart</v>
       </c>
       <c r="B6">
-        <v>16</v>
+        <v>3.2</v>
       </c>
       <c r="C6" t="str">
-        <v>16 Thousands (FTE)</v>
+        <v>3.2 Millions of Titles / Year</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -3214,10 +3215,10 @@
         <v>IAA</v>
       </c>
       <c r="B7">
-        <v>7</v>
+        <v>2.1</v>
       </c>
       <c r="C7" t="str">
-        <v>7 Thousands (FTE)</v>
+        <v>2.1 Millions of Titles / Year</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -3243,10 +3244,10 @@
         <v>Manheim</v>
       </c>
       <c r="B8">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C8" t="str">
-        <v>20 Thousands (FTE)</v>
+        <v>7 Millions of Titles / Year</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -3272,10 +3273,10 @@
         <v>OpenLane</v>
       </c>
       <c r="B9">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="C9" t="str">
-        <v>2.2 Thousands (FTE)</v>
+        <v>1.3 Millions of Titles / Year</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -3301,10 +3302,10 @@
         <v>ACV</v>
       </c>
       <c r="B10">
-        <v>1.7</v>
+        <v>0.55</v>
       </c>
       <c r="C10" t="str">
-        <v>1.7 Thousands (FTE)</v>
+        <v>0.55 Millions of Titles / Year</v>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -3330,10 +3331,10 @@
         <v>CarMax</v>
       </c>
       <c r="B11">
-        <v>28</v>
+        <v>1.8</v>
       </c>
       <c r="C11" t="str">
-        <v>28 Thousands (FTE)</v>
+        <v>1.8 Millions of Titles / Year</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -3359,10 +3360,10 @@
         <v>Carvana</v>
       </c>
       <c r="B12">
-        <v>15</v>
+        <v>0.8</v>
       </c>
       <c r="C12" t="str">
-        <v>15 Thousands (FTE)</v>
+        <v>0.8 Millions of Titles / Year</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -3501,28 +3502,28 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" t="str">
-        <v>Total Employees</v>
+        <v>Title Processing — All Channels</v>
       </c>
       <c r="B17">
-        <v>16</v>
+        <v>3.2</v>
       </c>
       <c r="C17">
+        <v>2.1</v>
+      </c>
+      <c r="D17">
         <v>7</v>
       </c>
-      <c r="D17">
-        <v>20</v>
-      </c>
       <c r="E17">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="F17">
-        <v>1.7</v>
+        <v>0.55</v>
       </c>
       <c r="G17">
-        <v>28</v>
+        <v>1.8</v>
       </c>
       <c r="H17">
-        <v>15</v>
+        <v>0.8</v>
       </c>
       <c r="I17" t="str">
         <v>N/A</v>
@@ -3533,28 +3534,28 @@
         <v>Unit</v>
       </c>
       <c r="B18" t="str">
-        <v>Thousands (FTE)</v>
+        <v>Millions of Titles / Year</v>
       </c>
       <c r="C18" t="str">
-        <v>Thousands (FTE)</v>
+        <v>Millions of Titles / Year</v>
       </c>
       <c r="D18" t="str">
-        <v>Thousands (FTE)</v>
+        <v>Millions of Titles / Year</v>
       </c>
       <c r="E18" t="str">
-        <v>Thousands (FTE)</v>
+        <v>Millions of Titles / Year</v>
       </c>
       <c r="F18" t="str">
-        <v>Thousands (FTE)</v>
+        <v>Millions of Titles / Year</v>
       </c>
       <c r="G18" t="str">
-        <v>Thousands (FTE)</v>
+        <v>Millions of Titles / Year</v>
       </c>
       <c r="H18" t="str">
-        <v>Thousands (FTE)</v>
+        <v>Millions of Titles / Year</v>
       </c>
       <c r="I18" t="str">
-        <v>Thousands (FTE)</v>
+        <v>Millions of Titles / Year</v>
       </c>
     </row>
   </sheetData>
@@ -3588,7 +3589,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" t="str">
-        <v>Glassdoor Employee Rating</v>
+        <v>Total Employees</v>
       </c>
       <c r="B1" t="str">
         <v/>
@@ -3617,7 +3618,7 @@
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" t="str">
-        <v>Unit: Rating (out of 5.0)   |   Aggregate employee satisfaction score, Glassdoor.com, 2024.</v>
+        <v>Unit: Thousands (FTE)   |   Full-time equivalent headcount, 2024. eBay Motors employees not separately reportable.</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -3707,7 +3708,7 @@
         <v>Company</v>
       </c>
       <c r="B5" t="str">
-        <v>Value (Rating (out of 5.0))</v>
+        <v>Value (Thousands (FTE))</v>
       </c>
       <c r="C5" t="str">
         <v>Notes</v>
@@ -3736,10 +3737,10 @@
         <v>Copart</v>
       </c>
       <c r="B6">
-        <v>3.9</v>
+        <v>16</v>
       </c>
       <c r="C6" t="str">
-        <v>3.9 Rating (out of 5.0)</v>
+        <v>16 Thousands (FTE)</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -3765,10 +3766,10 @@
         <v>IAA</v>
       </c>
       <c r="B7">
-        <v>3.4</v>
+        <v>7</v>
       </c>
       <c r="C7" t="str">
-        <v>3.4 Rating (out of 5.0)</v>
+        <v>7 Thousands (FTE)</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -3794,10 +3795,10 @@
         <v>Manheim</v>
       </c>
       <c r="B8">
-        <v>3.7</v>
+        <v>20</v>
       </c>
       <c r="C8" t="str">
-        <v>3.7 Rating (out of 5.0)</v>
+        <v>20 Thousands (FTE)</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -3823,10 +3824,10 @@
         <v>OpenLane</v>
       </c>
       <c r="B9">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="C9" t="str">
-        <v>3.5 Rating (out of 5.0)</v>
+        <v>2.2 Thousands (FTE)</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -3852,10 +3853,10 @@
         <v>ACV</v>
       </c>
       <c r="B10">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="C10" t="str">
-        <v>3.9 Rating (out of 5.0)</v>
+        <v>1.7 Thousands (FTE)</v>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -3881,10 +3882,10 @@
         <v>CarMax</v>
       </c>
       <c r="B11">
-        <v>3.9</v>
+        <v>28</v>
       </c>
       <c r="C11" t="str">
-        <v>3.9 Rating (out of 5.0)</v>
+        <v>28 Thousands (FTE)</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -3910,10 +3911,10 @@
         <v>Carvana</v>
       </c>
       <c r="B12">
-        <v>3.3</v>
+        <v>15</v>
       </c>
       <c r="C12" t="str">
-        <v>3.3 Rating (out of 5.0)</v>
+        <v>15 Thousands (FTE)</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -3938,11 +3939,11 @@
       <c r="A13" t="str">
         <v>eBay Motors</v>
       </c>
-      <c r="B13">
-        <v>3.8</v>
+      <c r="B13" t="str">
+        <v>N/A</v>
       </c>
       <c r="C13" t="str">
-        <v>3.8 Rating (out of 5.0)</v>
+        <v>Not applicable / not publicly reported</v>
       </c>
       <c r="D13" t="str">
         <v/>
@@ -4052,31 +4053,31 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" t="str">
-        <v>Glassdoor Employee Rating</v>
+        <v>Total Employees</v>
       </c>
       <c r="B17">
-        <v>3.9</v>
+        <v>16</v>
       </c>
       <c r="C17">
-        <v>3.4</v>
+        <v>7</v>
       </c>
       <c r="D17">
-        <v>3.7</v>
+        <v>20</v>
       </c>
       <c r="E17">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="F17">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="G17">
-        <v>3.9</v>
+        <v>28</v>
       </c>
       <c r="H17">
-        <v>3.3</v>
-      </c>
-      <c r="I17">
-        <v>3.8</v>
+        <v>15</v>
+      </c>
+      <c r="I17" t="str">
+        <v>N/A</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -4084,28 +4085,28 @@
         <v>Unit</v>
       </c>
       <c r="B18" t="str">
-        <v>Rating (out of 5.0)</v>
+        <v>Thousands (FTE)</v>
       </c>
       <c r="C18" t="str">
-        <v>Rating (out of 5.0)</v>
+        <v>Thousands (FTE)</v>
       </c>
       <c r="D18" t="str">
-        <v>Rating (out of 5.0)</v>
+        <v>Thousands (FTE)</v>
       </c>
       <c r="E18" t="str">
-        <v>Rating (out of 5.0)</v>
+        <v>Thousands (FTE)</v>
       </c>
       <c r="F18" t="str">
-        <v>Rating (out of 5.0)</v>
+        <v>Thousands (FTE)</v>
       </c>
       <c r="G18" t="str">
-        <v>Rating (out of 5.0)</v>
+        <v>Thousands (FTE)</v>
       </c>
       <c r="H18" t="str">
-        <v>Rating (out of 5.0)</v>
+        <v>Thousands (FTE)</v>
       </c>
       <c r="I18" t="str">
-        <v>Rating (out of 5.0)</v>
+        <v>Thousands (FTE)</v>
       </c>
     </row>
   </sheetData>
@@ -4139,7 +4140,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" t="str">
-        <v>Years in Operation</v>
+        <v>Glassdoor Employee Rating</v>
       </c>
       <c r="B1" t="str">
         <v/>
@@ -4168,7 +4169,7 @@
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" t="str">
-        <v>Unit: Years (as of 2024)   |   Continuous industry operation based on founding year.</v>
+        <v>Unit: Rating (out of 5.0)   |   Aggregate employee satisfaction score, Glassdoor.com, 2024.</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -4258,7 +4259,7 @@
         <v>Company</v>
       </c>
       <c r="B5" t="str">
-        <v>Value (Years (as of 2024))</v>
+        <v>Value (Rating (out of 5.0))</v>
       </c>
       <c r="C5" t="str">
         <v>Notes</v>
@@ -4287,10 +4288,10 @@
         <v>Copart</v>
       </c>
       <c r="B6">
-        <v>42</v>
+        <v>3.9</v>
       </c>
       <c r="C6" t="str">
-        <v>42 Years (as of 2024)</v>
+        <v>3.9 Rating (out of 5.0)</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -4316,10 +4317,10 @@
         <v>IAA</v>
       </c>
       <c r="B7">
-        <v>43</v>
+        <v>3.4</v>
       </c>
       <c r="C7" t="str">
-        <v>43 Years (as of 2024)</v>
+        <v>3.4 Rating (out of 5.0)</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -4345,10 +4346,10 @@
         <v>Manheim</v>
       </c>
       <c r="B8">
-        <v>79</v>
+        <v>3.7</v>
       </c>
       <c r="C8" t="str">
-        <v>79 Years (as of 2024)</v>
+        <v>3.7 Rating (out of 5.0)</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -4374,10 +4375,10 @@
         <v>OpenLane</v>
       </c>
       <c r="B9">
-        <v>35</v>
+        <v>3.5</v>
       </c>
       <c r="C9" t="str">
-        <v>35 Years (as of 2024)</v>
+        <v>3.5 Rating (out of 5.0)</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -4403,10 +4404,10 @@
         <v>ACV</v>
       </c>
       <c r="B10">
-        <v>10</v>
+        <v>3.9</v>
       </c>
       <c r="C10" t="str">
-        <v>10 Years (as of 2024)</v>
+        <v>3.9 Rating (out of 5.0)</v>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -4432,10 +4433,10 @@
         <v>CarMax</v>
       </c>
       <c r="B11">
-        <v>31</v>
+        <v>3.9</v>
       </c>
       <c r="C11" t="str">
-        <v>31 Years (as of 2024)</v>
+        <v>3.9 Rating (out of 5.0)</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -4461,10 +4462,10 @@
         <v>Carvana</v>
       </c>
       <c r="B12">
-        <v>12</v>
+        <v>3.3</v>
       </c>
       <c r="C12" t="str">
-        <v>12 Years (as of 2024)</v>
+        <v>3.3 Rating (out of 5.0)</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -4490,10 +4491,10 @@
         <v>eBay Motors</v>
       </c>
       <c r="B13">
-        <v>25</v>
+        <v>3.8</v>
       </c>
       <c r="C13" t="str">
-        <v>25 Years (as of 2024)</v>
+        <v>3.8 Rating (out of 5.0)</v>
       </c>
       <c r="D13" t="str">
         <v/>
@@ -4603,31 +4604,31 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" t="str">
-        <v>Years in Operation</v>
+        <v>Glassdoor Employee Rating</v>
       </c>
       <c r="B17">
-        <v>42</v>
+        <v>3.9</v>
       </c>
       <c r="C17">
-        <v>43</v>
+        <v>3.4</v>
       </c>
       <c r="D17">
-        <v>79</v>
+        <v>3.7</v>
       </c>
       <c r="E17">
-        <v>35</v>
+        <v>3.5</v>
       </c>
       <c r="F17">
-        <v>10</v>
+        <v>3.9</v>
       </c>
       <c r="G17">
-        <v>31</v>
+        <v>3.9</v>
       </c>
       <c r="H17">
-        <v>12</v>
+        <v>3.3</v>
       </c>
       <c r="I17">
-        <v>25</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -4635,28 +4636,28 @@
         <v>Unit</v>
       </c>
       <c r="B18" t="str">
-        <v>Years (as of 2024)</v>
+        <v>Rating (out of 5.0)</v>
       </c>
       <c r="C18" t="str">
-        <v>Years (as of 2024)</v>
+        <v>Rating (out of 5.0)</v>
       </c>
       <c r="D18" t="str">
-        <v>Years (as of 2024)</v>
+        <v>Rating (out of 5.0)</v>
       </c>
       <c r="E18" t="str">
-        <v>Years (as of 2024)</v>
+        <v>Rating (out of 5.0)</v>
       </c>
       <c r="F18" t="str">
-        <v>Years (as of 2024)</v>
+        <v>Rating (out of 5.0)</v>
       </c>
       <c r="G18" t="str">
-        <v>Years (as of 2024)</v>
+        <v>Rating (out of 5.0)</v>
       </c>
       <c r="H18" t="str">
-        <v>Years (as of 2024)</v>
+        <v>Rating (out of 5.0)</v>
       </c>
       <c r="I18" t="str">
-        <v>Years (as of 2024)</v>
+        <v>Rating (out of 5.0)</v>
       </c>
     </row>
   </sheetData>
@@ -4690,7 +4691,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" t="str">
-        <v>Main App Rating (iOS)</v>
+        <v>Years in Operation</v>
       </c>
       <c r="B1" t="str">
         <v/>
@@ -4719,7 +4720,7 @@
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" t="str">
-        <v>Unit: Rating (out of 5.0)   |   iOS App Store buyer/seller platform rating, 2024.</v>
+        <v>Unit: Years (as of 2024)   |   Continuous industry operation based on founding year.</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -4809,7 +4810,7 @@
         <v>Company</v>
       </c>
       <c r="B5" t="str">
-        <v>Value (Rating (out of 5.0))</v>
+        <v>Value (Years (as of 2024))</v>
       </c>
       <c r="C5" t="str">
         <v>Notes</v>
@@ -4838,10 +4839,10 @@
         <v>Copart</v>
       </c>
       <c r="B6">
-        <v>4.8</v>
+        <v>42</v>
       </c>
       <c r="C6" t="str">
-        <v>4.8 Rating (out of 5.0)</v>
+        <v>42 Years (as of 2024)</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -4867,10 +4868,10 @@
         <v>IAA</v>
       </c>
       <c r="B7">
-        <v>4.3</v>
+        <v>43</v>
       </c>
       <c r="C7" t="str">
-        <v>4.3 Rating (out of 5.0)</v>
+        <v>43 Years (as of 2024)</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -4896,10 +4897,10 @@
         <v>Manheim</v>
       </c>
       <c r="B8">
-        <v>3.9</v>
+        <v>79</v>
       </c>
       <c r="C8" t="str">
-        <v>3.9 Rating (out of 5.0)</v>
+        <v>79 Years (as of 2024)</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -4925,10 +4926,10 @@
         <v>OpenLane</v>
       </c>
       <c r="B9">
-        <v>3.7</v>
+        <v>35</v>
       </c>
       <c r="C9" t="str">
-        <v>3.7 Rating (out of 5.0)</v>
+        <v>35 Years (as of 2024)</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -4954,10 +4955,10 @@
         <v>ACV</v>
       </c>
       <c r="B10">
-        <v>4.6</v>
+        <v>10</v>
       </c>
       <c r="C10" t="str">
-        <v>4.6 Rating (out of 5.0)</v>
+        <v>10 Years (as of 2024)</v>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -4983,10 +4984,10 @@
         <v>CarMax</v>
       </c>
       <c r="B11">
-        <v>4.8</v>
+        <v>31</v>
       </c>
       <c r="C11" t="str">
-        <v>4.8 Rating (out of 5.0)</v>
+        <v>31 Years (as of 2024)</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -5012,10 +5013,10 @@
         <v>Carvana</v>
       </c>
       <c r="B12">
-        <v>4.8</v>
+        <v>12</v>
       </c>
       <c r="C12" t="str">
-        <v>4.8 Rating (out of 5.0)</v>
+        <v>12 Years (as of 2024)</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -5041,10 +5042,10 @@
         <v>eBay Motors</v>
       </c>
       <c r="B13">
-        <v>4.4</v>
+        <v>25</v>
       </c>
       <c r="C13" t="str">
-        <v>4.4 Rating (out of 5.0)</v>
+        <v>25 Years (as of 2024)</v>
       </c>
       <c r="D13" t="str">
         <v/>
@@ -5154,31 +5155,31 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" t="str">
-        <v>Main App Rating (iOS)</v>
+        <v>Years in Operation</v>
       </c>
       <c r="B17">
-        <v>4.8</v>
+        <v>42</v>
       </c>
       <c r="C17">
-        <v>4.3</v>
+        <v>43</v>
       </c>
       <c r="D17">
-        <v>3.9</v>
+        <v>79</v>
       </c>
       <c r="E17">
-        <v>3.7</v>
+        <v>35</v>
       </c>
       <c r="F17">
-        <v>4.6</v>
+        <v>10</v>
       </c>
       <c r="G17">
-        <v>4.8</v>
+        <v>31</v>
       </c>
       <c r="H17">
-        <v>4.8</v>
+        <v>12</v>
       </c>
       <c r="I17">
-        <v>4.4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -5186,28 +5187,28 @@
         <v>Unit</v>
       </c>
       <c r="B18" t="str">
-        <v>Rating (out of 5.0)</v>
+        <v>Years (as of 2024)</v>
       </c>
       <c r="C18" t="str">
-        <v>Rating (out of 5.0)</v>
+        <v>Years (as of 2024)</v>
       </c>
       <c r="D18" t="str">
-        <v>Rating (out of 5.0)</v>
+        <v>Years (as of 2024)</v>
       </c>
       <c r="E18" t="str">
-        <v>Rating (out of 5.0)</v>
+        <v>Years (as of 2024)</v>
       </c>
       <c r="F18" t="str">
-        <v>Rating (out of 5.0)</v>
+        <v>Years (as of 2024)</v>
       </c>
       <c r="G18" t="str">
-        <v>Rating (out of 5.0)</v>
+        <v>Years (as of 2024)</v>
       </c>
       <c r="H18" t="str">
-        <v>Rating (out of 5.0)</v>
+        <v>Years (as of 2024)</v>
       </c>
       <c r="I18" t="str">
-        <v>Rating (out of 5.0)</v>
+        <v>Years (as of 2024)</v>
       </c>
     </row>
   </sheetData>
@@ -5241,7 +5242,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" t="str">
-        <v>Main App Downloads</v>
+        <v>Main App Rating (iOS)</v>
       </c>
       <c r="B1" t="str">
         <v/>
@@ -5270,7 +5271,7 @@
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" t="str">
-        <v>Unit: Millions (cumulative)   |   Combined iOS + Android total downloads, 2024. eBay Motors app counted separately.</v>
+        <v>Unit: Rating (out of 5.0)   |   iOS App Store buyer/seller platform rating, 2024.</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -5360,7 +5361,7 @@
         <v>Company</v>
       </c>
       <c r="B5" t="str">
-        <v>Value (Millions (cumulative))</v>
+        <v>Value (Rating (out of 5.0))</v>
       </c>
       <c r="C5" t="str">
         <v>Notes</v>
@@ -5389,10 +5390,10 @@
         <v>Copart</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="C6" t="str">
-        <v>5 Millions (cumulative)</v>
+        <v>4.8 Rating (out of 5.0)</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -5418,10 +5419,10 @@
         <v>IAA</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>4.3</v>
       </c>
       <c r="C7" t="str">
-        <v>2 Millions (cumulative)</v>
+        <v>4.3 Rating (out of 5.0)</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -5447,10 +5448,10 @@
         <v>Manheim</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="C8" t="str">
-        <v>1 Millions (cumulative)</v>
+        <v>3.9 Rating (out of 5.0)</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -5476,10 +5477,10 @@
         <v>OpenLane</v>
       </c>
       <c r="B9">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="C9" t="str">
-        <v>0.5 Millions (cumulative)</v>
+        <v>3.7 Rating (out of 5.0)</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -5505,10 +5506,10 @@
         <v>ACV</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="C10" t="str">
-        <v>1 Millions (cumulative)</v>
+        <v>4.6 Rating (out of 5.0)</v>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -5534,10 +5535,10 @@
         <v>CarMax</v>
       </c>
       <c r="B11">
-        <v>10</v>
+        <v>4.8</v>
       </c>
       <c r="C11" t="str">
-        <v>10 Millions (cumulative)</v>
+        <v>4.8 Rating (out of 5.0)</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -5563,10 +5564,10 @@
         <v>Carvana</v>
       </c>
       <c r="B12">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="C12" t="str">
-        <v>8 Millions (cumulative)</v>
+        <v>4.8 Rating (out of 5.0)</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -5592,10 +5593,10 @@
         <v>eBay Motors</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="C13" t="str">
-        <v>5 Millions (cumulative)</v>
+        <v>4.4 Rating (out of 5.0)</v>
       </c>
       <c r="D13" t="str">
         <v/>
@@ -5705,31 +5706,31 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" t="str">
-        <v>Main App Downloads</v>
+        <v>Main App Rating (iOS)</v>
       </c>
       <c r="B17">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>4.3</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="E17">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="G17">
-        <v>10</v>
+        <v>4.8</v>
       </c>
       <c r="H17">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="I17">
-        <v>5</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -5737,28 +5738,28 @@
         <v>Unit</v>
       </c>
       <c r="B18" t="str">
-        <v>Millions (cumulative)</v>
+        <v>Rating (out of 5.0)</v>
       </c>
       <c r="C18" t="str">
-        <v>Millions (cumulative)</v>
+        <v>Rating (out of 5.0)</v>
       </c>
       <c r="D18" t="str">
-        <v>Millions (cumulative)</v>
+        <v>Rating (out of 5.0)</v>
       </c>
       <c r="E18" t="str">
-        <v>Millions (cumulative)</v>
+        <v>Rating (out of 5.0)</v>
       </c>
       <c r="F18" t="str">
-        <v>Millions (cumulative)</v>
+        <v>Rating (out of 5.0)</v>
       </c>
       <c r="G18" t="str">
-        <v>Millions (cumulative)</v>
+        <v>Rating (out of 5.0)</v>
       </c>
       <c r="H18" t="str">
-        <v>Millions (cumulative)</v>
+        <v>Rating (out of 5.0)</v>
       </c>
       <c r="I18" t="str">
-        <v>Millions (cumulative)</v>
+        <v>Rating (out of 5.0)</v>
       </c>
     </row>
   </sheetData>
@@ -5792,7 +5793,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" t="str">
-        <v>Driver App Rating (iOS)</v>
+        <v>Main App Downloads</v>
       </c>
       <c r="B1" t="str">
         <v/>
@@ -5821,7 +5822,7 @@
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" t="str">
-        <v>Unit: Rating (out of 5.0)   |   Dedicated driver/transport app iOS rating, 2024. N/A where no dedicated driver app exists.</v>
+        <v>Unit: Millions (cumulative)   |   Combined iOS + Android total downloads, 2024. eBay Motors app counted separately.</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -5911,7 +5912,7 @@
         <v>Company</v>
       </c>
       <c r="B5" t="str">
-        <v>Value (Rating (out of 5.0))</v>
+        <v>Value (Millions (cumulative))</v>
       </c>
       <c r="C5" t="str">
         <v>Notes</v>
@@ -5940,10 +5941,10 @@
         <v>Copart</v>
       </c>
       <c r="B6">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="C6" t="str">
-        <v>4.5 Rating (out of 5.0)</v>
+        <v>5 Millions (cumulative)</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -5969,10 +5970,10 @@
         <v>IAA</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C7" t="str">
-        <v>4 Rating (out of 5.0)</v>
+        <v>2 Millions (cumulative)</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -5998,10 +5999,10 @@
         <v>Manheim</v>
       </c>
       <c r="B8">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="C8" t="str">
-        <v>3.8 Rating (out of 5.0)</v>
+        <v>1 Millions (cumulative)</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -6026,11 +6027,11 @@
       <c r="A9" t="str">
         <v>OpenLane</v>
       </c>
-      <c r="B9" t="str">
-        <v>N/A</v>
+      <c r="B9">
+        <v>0.5</v>
       </c>
       <c r="C9" t="str">
-        <v>Not applicable / not publicly reported</v>
+        <v>0.5 Millions (cumulative)</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -6056,10 +6057,10 @@
         <v>ACV</v>
       </c>
       <c r="B10">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="str">
-        <v>4.2 Rating (out of 5.0)</v>
+        <v>1 Millions (cumulative)</v>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -6085,10 +6086,10 @@
         <v>CarMax</v>
       </c>
       <c r="B11">
-        <v>4.3</v>
+        <v>10</v>
       </c>
       <c r="C11" t="str">
-        <v>4.3 Rating (out of 5.0)</v>
+        <v>10 Millions (cumulative)</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -6114,10 +6115,10 @@
         <v>Carvana</v>
       </c>
       <c r="B12">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="C12" t="str">
-        <v>4.5 Rating (out of 5.0)</v>
+        <v>8 Millions (cumulative)</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -6142,11 +6143,11 @@
       <c r="A13" t="str">
         <v>eBay Motors</v>
       </c>
-      <c r="B13" t="str">
-        <v>N/A</v>
+      <c r="B13">
+        <v>5</v>
       </c>
       <c r="C13" t="str">
-        <v>Not applicable / not publicly reported</v>
+        <v>5 Millions (cumulative)</v>
       </c>
       <c r="D13" t="str">
         <v/>
@@ -6256,31 +6257,31 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" t="str">
-        <v>Driver App Rating (iOS)</v>
+        <v>Main App Downloads</v>
       </c>
       <c r="B17">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="C17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D17">
-        <v>3.8</v>
-      </c>
-      <c r="E17" t="str">
-        <v>N/A</v>
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>0.5</v>
       </c>
       <c r="F17">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="G17">
-        <v>4.3</v>
+        <v>10</v>
       </c>
       <c r="H17">
-        <v>4.5</v>
-      </c>
-      <c r="I17" t="str">
-        <v>N/A</v>
+        <v>8</v>
+      </c>
+      <c r="I17">
+        <v>5</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -6288,28 +6289,28 @@
         <v>Unit</v>
       </c>
       <c r="B18" t="str">
-        <v>Rating (out of 5.0)</v>
+        <v>Millions (cumulative)</v>
       </c>
       <c r="C18" t="str">
-        <v>Rating (out of 5.0)</v>
+        <v>Millions (cumulative)</v>
       </c>
       <c r="D18" t="str">
-        <v>Rating (out of 5.0)</v>
+        <v>Millions (cumulative)</v>
       </c>
       <c r="E18" t="str">
-        <v>Rating (out of 5.0)</v>
+        <v>Millions (cumulative)</v>
       </c>
       <c r="F18" t="str">
-        <v>Rating (out of 5.0)</v>
+        <v>Millions (cumulative)</v>
       </c>
       <c r="G18" t="str">
-        <v>Rating (out of 5.0)</v>
+        <v>Millions (cumulative)</v>
       </c>
       <c r="H18" t="str">
-        <v>Rating (out of 5.0)</v>
+        <v>Millions (cumulative)</v>
       </c>
       <c r="I18" t="str">
-        <v>Rating (out of 5.0)</v>
+        <v>Millions (cumulative)</v>
       </c>
     </row>
   </sheetData>
@@ -6343,7 +6344,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" t="str">
-        <v>Driver App Downloads</v>
+        <v>Driver App Rating (iOS)</v>
       </c>
       <c r="B1" t="str">
         <v/>
@@ -6372,7 +6373,7 @@
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" t="str">
-        <v>Unit: Millions (cumulative)   |   Driver/transport app combined iOS + Android downloads, 2024. N/A where no dedicated app exists.</v>
+        <v>Unit: Rating (out of 5.0)   |   Dedicated driver/transport app iOS rating, 2024. N/A where no dedicated driver app exists.</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -6462,7 +6463,7 @@
         <v>Company</v>
       </c>
       <c r="B5" t="str">
-        <v>Value (Millions (cumulative))</v>
+        <v>Value (Rating (out of 5.0))</v>
       </c>
       <c r="C5" t="str">
         <v>Notes</v>
@@ -6491,10 +6492,10 @@
         <v>Copart</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="C6" t="str">
-        <v>1 Millions (cumulative)</v>
+        <v>4.5 Rating (out of 5.0)</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -6520,10 +6521,10 @@
         <v>IAA</v>
       </c>
       <c r="B7">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="C7" t="str">
-        <v>0.5 Millions (cumulative)</v>
+        <v>4 Rating (out of 5.0)</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -6549,10 +6550,10 @@
         <v>Manheim</v>
       </c>
       <c r="B8">
-        <v>0.3</v>
+        <v>3.8</v>
       </c>
       <c r="C8" t="str">
-        <v>0.3 Millions (cumulative)</v>
+        <v>3.8 Rating (out of 5.0)</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -6607,10 +6608,10 @@
         <v>ACV</v>
       </c>
       <c r="B10">
-        <v>0.4</v>
+        <v>4.2</v>
       </c>
       <c r="C10" t="str">
-        <v>0.4 Millions (cumulative)</v>
+        <v>4.2 Rating (out of 5.0)</v>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -6636,10 +6637,10 @@
         <v>CarMax</v>
       </c>
       <c r="B11">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="C11" t="str">
-        <v>0.8 Millions (cumulative)</v>
+        <v>4.3 Rating (out of 5.0)</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -6665,10 +6666,10 @@
         <v>Carvana</v>
       </c>
       <c r="B12">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="C12" t="str">
-        <v>1.2 Millions (cumulative)</v>
+        <v>4.5 Rating (out of 5.0)</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -6807,28 +6808,28 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" t="str">
-        <v>Driver App Downloads</v>
+        <v>Driver App Rating (iOS)</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="C17">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="D17">
-        <v>0.3</v>
+        <v>3.8</v>
       </c>
       <c r="E17" t="str">
         <v>N/A</v>
       </c>
       <c r="F17">
-        <v>0.4</v>
+        <v>4.2</v>
       </c>
       <c r="G17">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="H17">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="I17" t="str">
         <v>N/A</v>
@@ -6839,28 +6840,28 @@
         <v>Unit</v>
       </c>
       <c r="B18" t="str">
-        <v>Millions (cumulative)</v>
+        <v>Rating (out of 5.0)</v>
       </c>
       <c r="C18" t="str">
-        <v>Millions (cumulative)</v>
+        <v>Rating (out of 5.0)</v>
       </c>
       <c r="D18" t="str">
-        <v>Millions (cumulative)</v>
+        <v>Rating (out of 5.0)</v>
       </c>
       <c r="E18" t="str">
-        <v>Millions (cumulative)</v>
+        <v>Rating (out of 5.0)</v>
       </c>
       <c r="F18" t="str">
-        <v>Millions (cumulative)</v>
+        <v>Rating (out of 5.0)</v>
       </c>
       <c r="G18" t="str">
-        <v>Millions (cumulative)</v>
+        <v>Rating (out of 5.0)</v>
       </c>
       <c r="H18" t="str">
-        <v>Millions (cumulative)</v>
+        <v>Rating (out of 5.0)</v>
       </c>
       <c r="I18" t="str">
-        <v>Millions (cumulative)</v>
+        <v>Rating (out of 5.0)</v>
       </c>
     </row>
   </sheetData>
@@ -6879,22 +6880,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:C30"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="42.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+    <col min="1" max="1" width="36.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="90.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" t="str">
-        <v>Annual Revenue</v>
+        <v>Copart Competitive Dashboard — Data Sources &amp; Citations</v>
       </c>
       <c r="B1" t="str">
         <v/>
@@ -6902,51 +6897,15 @@
       <c r="C1" t="str">
         <v/>
       </c>
-      <c r="D1" t="str">
-        <v/>
-      </c>
-      <c r="E1" t="str">
-        <v/>
-      </c>
-      <c r="F1" t="str">
-        <v/>
-      </c>
-      <c r="G1" t="str">
-        <v/>
-      </c>
-      <c r="H1" t="str">
-        <v/>
-      </c>
-      <c r="I1" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="2" ht="36" customHeight="1">
+    </row>
+    <row r="2" ht="28" customHeight="1">
       <c r="A2" t="str">
-        <v>Unit: USD Billions   |   Most recent fiscal year (FY2024). CarMax &amp; Carvana include retail sales. eBay Motors is estimated.</v>
+        <v>All data is directional and approximate — intended for presentation use, not investment decisions. Sources accessed 2024.</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2" t="str">
-        <v/>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
-      <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2" t="str">
         <v/>
       </c>
     </row>
@@ -6960,470 +6919,301 @@
       <c r="C3" t="str">
         <v/>
       </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
+    </row>
+    <row r="4" ht="24" customHeight="1">
       <c r="A4" t="str">
-        <v>VERTICAL LAYOUT</v>
+        <v>Metric</v>
       </c>
       <c r="B4" t="str">
-        <v/>
+        <v>Unit</v>
       </c>
       <c r="C4" t="str">
-        <v/>
-      </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
+        <v>Source / Citation</v>
+      </c>
+    </row>
+    <row r="5" ht="52" customHeight="1">
       <c r="A5" t="str">
-        <v>Company</v>
+        <v>Annual Revenue</v>
       </c>
       <c r="B5" t="str">
-        <v>Value (USD Billions)</v>
+        <v>USD Billions</v>
       </c>
       <c r="C5" t="str">
-        <v>Notes</v>
-      </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
+        <v>Copart 10-K FY2024; RB Global (IAA) 10-K FY2024; Cox Automotive / Manheim press release; OPENLANE 10-K FY2024; ACV Auctions 10-K FY2024; CarMax 10-K FY2024; Carvana 10-K FY2024; eBay Inc. 10-K FY2024 (segment estimate).</v>
+      </c>
+    </row>
+    <row r="6" ht="52" customHeight="1">
       <c r="A6" t="str">
-        <v>Copart</v>
-      </c>
-      <c r="B6">
-        <v>4.19</v>
+        <v>Market Capitalization</v>
+      </c>
+      <c r="B6" t="str">
+        <v>USD Billions</v>
       </c>
       <c r="C6" t="str">
-        <v>4.19 USD Billions</v>
-      </c>
-      <c r="D6" t="str">
-        <v/>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
+        <v>Bloomberg / Yahoo Finance market-cap data as of 31 Dec 2024. Manheim is a Cox Automotive division (privately held). eBay Motors is a division of eBay Inc. and not separately traded.</v>
+      </c>
+    </row>
+    <row r="7" ht="52" customHeight="1">
       <c r="A7" t="str">
-        <v>IAA</v>
-      </c>
-      <c r="B7">
-        <v>4.06</v>
+        <v>Capital Expenditure</v>
+      </c>
+      <c r="B7" t="str">
+        <v>USD Billions</v>
       </c>
       <c r="C7" t="str">
-        <v>4.06 USD Billions</v>
-      </c>
-      <c r="D7" t="str">
-        <v/>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
+        <v>Copart 10-K FY2024 (cash flow statement); RB Global 10-K FY2024; OPENLANE 10-K FY2024; ACV Auctions 10-K FY2024; CarMax 10-K FY2024; Carvana 10-K FY2024. Manheim capex not separately disclosed by Cox Automotive.</v>
+      </c>
+    </row>
+    <row r="8" ht="52" customHeight="1">
       <c r="A8" t="str">
-        <v>Manheim</v>
-      </c>
-      <c r="B8">
-        <v>4.5</v>
+        <v>Physical Locations</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Number of Sites</v>
       </c>
       <c r="C8" t="str">
-        <v>4.5 USD Billions</v>
-      </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
+        <v>Copart 10-K FY2024 (operations section); RB Global 10-K FY2024; Manheim press releases / Cox Automotive newsroom 2024; OPENLANE investor relations 2024; ACV Auctions — digital-only platform; CarMax 10-K FY2024; Carvana 10-K FY2024 (inspection/recondition centres); eBay Motors — digital marketplace.</v>
+      </c>
+    </row>
+    <row r="9" ht="52" customHeight="1">
       <c r="A9" t="str">
-        <v>OpenLane</v>
-      </c>
-      <c r="B9">
-        <v>0.91</v>
+        <v>Land Footprint</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Thousands of Acres</v>
       </c>
       <c r="C9" t="str">
-        <v>0.91 USD Billions</v>
-      </c>
-      <c r="D9" t="str">
-        <v/>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
+        <v>Copart 10-K FY2024 (properties section); RB Global 10-K FY2024; Manheim / Cox Automotive corporate fact sheet; OPENLANE corporate fact sheet; CarMax real estate disclosures 10-K FY2024; Carvana operations disclosures. ACV &amp; eBay Motors: near-zero physical footprint.</v>
+      </c>
+    </row>
+    <row r="10" ht="52" customHeight="1">
       <c r="A10" t="str">
-        <v>ACV</v>
-      </c>
-      <c r="B10">
-        <v>0.63</v>
+        <v>Countries of Operation</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Countries</v>
       </c>
       <c r="C10" t="str">
-        <v>0.63 USD Billions</v>
-      </c>
-      <c r="D10" t="str">
-        <v/>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
+        <v>Copart 10-K FY2024 (international segment); RB Global 10-K FY2024; Manheim international locations (Cox Automotive); OPENLANE / BacklotCars international; ACV Auctions operations disclosure; CarMax and Carvana US-only; eBay Motors active country count from eBay Inc. 10-K FY2024.</v>
+      </c>
+    </row>
+    <row r="11" ht="52" customHeight="1">
       <c r="A11" t="str">
-        <v>CarMax</v>
-      </c>
-      <c r="B11">
-        <v>26.5</v>
+        <v>Vehicles Auctioned / Available</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Millions / Year</v>
       </c>
       <c r="C11" t="str">
-        <v>26.5 USD Billions</v>
-      </c>
-      <c r="D11" t="str">
-        <v/>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
+        <v>Copart 10-K FY2024 (volume metrics); RB Global 10-K FY2024; Manheim / Cox Automotive 2024 Used Car Market Report; OPENLANE 10-K FY2024; ACV Auctions 10-K FY2024; CarMax and Carvana retail sales volume from respective 10-Ks; eBay Motors listing volume estimate from eBay Inc. investor materials.</v>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1">
       <c r="A12" t="str">
-        <v>Carvana</v>
-      </c>
-      <c r="B12">
-        <v>13.7</v>
+        <v>Vehicles Sold Annually</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Millions / Year</v>
       </c>
       <c r="C12" t="str">
-        <v>13.7 USD Billions</v>
-      </c>
-      <c r="D12" t="str">
-        <v/>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
+        <v>Copart 10-K FY2024; RB Global 10-K FY2024; Manheim 2024 Used Car Market Report (Cox Automotive); OPENLANE 10-K FY2024; ACV Auctions 10-K FY2024; CarMax 10-K FY2024 (units sold); Carvana 10-K FY2024 (units sold); eBay Motors GMV / listing conversion estimate.</v>
+      </c>
+    </row>
+    <row r="13" ht="52" customHeight="1">
       <c r="A13" t="str">
-        <v>eBay Motors</v>
-      </c>
-      <c r="B13">
-        <v>1.8</v>
+        <v>Average Daily Inventory</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Thousands of Vehicles</v>
       </c>
       <c r="C13" t="str">
-        <v>1.8 USD Billions</v>
-      </c>
-      <c r="D13" t="str">
-        <v/>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="8" customHeight="1">
+        <v>Copart investor day presentation 2024; RB Global investor materials 2024; Manheim / Cox Automotive market data; OPENLANE investor relations; ACV Auctions investor materials; CarMax inventory disclosures; Carvana real-time inventory data; eBay Motors active listing count estimate.</v>
+      </c>
+    </row>
+    <row r="14" ht="52" customHeight="1">
       <c r="A14" t="str">
-        <v/>
+        <v>Towing &amp; Transporter Network</v>
       </c>
       <c r="B14" t="str">
-        <v/>
+        <v>Thousands of Providers / Vehicles</v>
       </c>
       <c r="C14" t="str">
-        <v/>
-      </c>
-      <c r="D14" t="str">
-        <v/>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
+        <v>Copart 10-K FY2024 and investor presentations; RB Global 10-K FY2024; Manheim / Cox Ready Logistics press releases; OPENLANE transport partner disclosures; ACV Auctions transport network; CarMax delivery fleet disclosures; Carvana 10-K FY2024 (owned delivery vehicles).</v>
+      </c>
+    </row>
+    <row r="15" ht="52" customHeight="1">
       <c r="A15" t="str">
-        <v>HORIZONTAL LAYOUT</v>
+        <v>Title Processing — All Channels</v>
       </c>
       <c r="B15" t="str">
-        <v/>
+        <v>Millions of Titles / Year</v>
       </c>
       <c r="C15" t="str">
-        <v/>
-      </c>
-      <c r="D15" t="str">
-        <v/>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1">
+        <v>Copart 10-K FY2024 (title services); RB Global 10-K FY2024; Manheim / Dealer Solutions title processing data; OPENLANE 10-K FY2024; ACV Auctions operational disclosures; CarMax 10-K FY2024 (unit sales × title rate); Carvana 10-K FY2024.</v>
+      </c>
+    </row>
+    <row r="16" ht="52" customHeight="1">
       <c r="A16" t="str">
-        <v>Metric</v>
+        <v>Total Employees</v>
       </c>
       <c r="B16" t="str">
-        <v>Copart</v>
+        <v>Thousands (FTE)</v>
       </c>
       <c r="C16" t="str">
-        <v>IAA</v>
-      </c>
-      <c r="D16" t="str">
-        <v>Manheim</v>
-      </c>
-      <c r="E16" t="str">
-        <v>OpenLane</v>
-      </c>
-      <c r="F16" t="str">
-        <v>ACV</v>
-      </c>
-      <c r="G16" t="str">
-        <v>CarMax</v>
-      </c>
-      <c r="H16" t="str">
-        <v>Carvana</v>
-      </c>
-      <c r="I16" t="str">
-        <v>eBay Motors</v>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
+        <v>Copart 10-K FY2024; RB Global 10-K FY2024; Cox Automotive / Manheim workforce data; OPENLANE 10-K FY2024; ACV Auctions 10-K FY2024; CarMax 10-K FY2024; Carvana 10-K FY2024; eBay Inc. 10-K FY2024 (total headcount; Motors division not separately disclosed).</v>
+      </c>
+    </row>
+    <row r="17" ht="52" customHeight="1">
       <c r="A17" t="str">
-        <v>Annual Revenue</v>
-      </c>
-      <c r="B17">
-        <v>4.19</v>
-      </c>
-      <c r="C17">
-        <v>4.06</v>
-      </c>
-      <c r="D17">
-        <v>4.5</v>
-      </c>
-      <c r="E17">
-        <v>0.91</v>
-      </c>
-      <c r="F17">
-        <v>0.63</v>
-      </c>
-      <c r="G17">
-        <v>26.5</v>
-      </c>
-      <c r="H17">
-        <v>13.7</v>
-      </c>
-      <c r="I17">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
+        <v>Glassdoor Employee Rating</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Rating (out of 5.0)</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Glassdoor.com company pages (accessed 2024): Copart, RB Global / IAA, Manheim, OPENLANE, ACV Auctions, CarMax, Carvana, eBay. Ratings are aggregate of all-time reviews weighted toward recent activity.</v>
+      </c>
+    </row>
+    <row r="18" ht="52" customHeight="1">
       <c r="A18" t="str">
-        <v>Unit</v>
+        <v>Years in Operation</v>
       </c>
       <c r="B18" t="str">
-        <v>USD Billions</v>
+        <v>Years (as of 2024)</v>
       </c>
       <c r="C18" t="str">
-        <v>USD Billions</v>
-      </c>
-      <c r="D18" t="str">
-        <v>USD Billions</v>
-      </c>
-      <c r="E18" t="str">
-        <v>USD Billions</v>
-      </c>
-      <c r="F18" t="str">
-        <v>USD Billions</v>
-      </c>
-      <c r="G18" t="str">
-        <v>USD Billions</v>
-      </c>
-      <c r="H18" t="str">
-        <v>USD Billions</v>
-      </c>
-      <c r="I18" t="str">
-        <v>USD Billions</v>
+        <v>Company founding years: Copart (1982); IAA/Insurance Auto Auctions (1982); Manheim (1945); OPENLANE/ADESA (1989); ACV Auctions (2014); CarMax (1993); Carvana (2012); eBay Motors within eBay (1999). Sources: company histories, SEC filings, Wikipedia.</v>
+      </c>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" t="str">
+        <v>Main App Rating (iOS)</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Rating (out of 5.0)</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Apple App Store ratings (accessed 2024): Copart Mobile, RB Global / IAA auction app, Manheim app, OPENLANE app, ACV Auctions app, CarMax app, Carvana app, eBay Motors app.</v>
+      </c>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" t="str">
+        <v>Main App Downloads</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Millions (cumulative)</v>
+      </c>
+      <c r="C20" t="str">
+        <v>App Annie / data.ai and Sensor Tower cumulative download estimates, 2024. iOS App Store + Google Play Store combined figures. Figures are directional estimates; exact numbers not publicly disclosed by platforms.</v>
+      </c>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" t="str">
+        <v>Driver App Rating (iOS)</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Rating (out of 5.0)</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Apple App Store ratings (accessed 2024): Copart Transport App, RB Global Transport App, Manheim Transport App, ACV Transport App, CarMax delivery driver app, Carvana driver app. OpenLane and eBay Motors do not offer dedicated driver apps.</v>
+      </c>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" t="str">
+        <v>Driver App Downloads</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Millions (cumulative)</v>
+      </c>
+      <c r="C22" t="str">
+        <v>App Annie / data.ai and Sensor Tower cumulative download estimates, 2024 (driver/transport app variants). Figures are directional estimates.</v>
+      </c>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" t="str">
+        <v>Registered Global Buyers</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Thousands of Accounts</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Copart 10-K FY2024 (member accounts); RB Global 10-K FY2024; Manheim dealer membership data; OPENLANE 10-K FY2024; ACV Auctions 10-K FY2024. CarMax, Carvana, and eBay Motors use consumer (B2C) models without equivalent registered buyer figures.</v>
+      </c>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" t="str">
+        <v>Buyer Countries</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Countries</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Copart 10-K FY2024 (international buyer segment); RB Global 10-K FY2024; Manheim international dealer data; OPENLANE international buyer data; ACV Auctions US + Canada; CarMax and Carvana US-only; eBay Motors international listing &amp; bidder data from eBay Inc. investor materials.</v>
+      </c>
+    </row>
+    <row r="25" ht="52" customHeight="1">
+      <c r="A25" t="str">
+        <v>Monthly Social &amp; Web Mentions</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Thousands / Month</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Brandwatch, Mention.com, and Sprout Social industry benchmark estimates, 2024. Includes Twitter/X, Reddit, LinkedIn, news articles, and automotive forums. Figures are estimates; exact counts require enterprise social listening contracts.</v>
+      </c>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" t="str">
+        <v>B2B Auction Mentions (Excl. Retail)</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Thousands / Month</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Same as "Monthly Social &amp; Web Mentions" with retail consumer brand noise filtered out using automotive dealer and insurance-segment keyword filters. CarMax and Carvana excluded (B2C-only context).</v>
+      </c>
+    </row>
+    <row r="27" ht="52" customHeight="1">
+      <c r="A27" t="str">
+        <v>YouTube Channel Subscribers</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Thousands of Subscribers</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Official YouTube channel subscriber counts (accessed 2024): Copart, RB Global / IAA, Manheim, OPENLANE, ACV Auctions, CarMax, Carvana, eBay Motors. Data sourced directly from YouTube channel pages.</v>
+      </c>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" t="str">
+        <v>Monthly YouTube Mentions</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Thousands / Month</v>
+      </c>
+      <c r="C28" t="str">
+        <v>TubeBuddy and vidIQ keyword analysis, 2024. Includes dedicated brand reviews, haul/flip videos, and creator references. High consumer-brand figures (CarMax, Carvana) reflect popular "car buying experience" content category.</v>
+      </c>
+    </row>
+    <row r="29" ht="52" customHeight="1">
+      <c r="A29" t="str">
+        <v>Estimated Monthly SEM Spend</v>
+      </c>
+      <c r="B29" t="str">
+        <v>USD Millions / Month</v>
+      </c>
+      <c r="C29" t="str">
+        <v>SEMrush and SpyFu paid search intelligence estimates, 2024. Not publicly disclosed by any company; figures are third-party estimates based on keyword auction data. Retail brands (CarMax, Carvana, eBay) spend significantly more due to high-intent consumer search volume.</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A14:I14"/>
-    <mergeCell ref="A15:I15"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C30"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -7445,7 +7235,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" t="str">
-        <v>Registered Global Buyers</v>
+        <v>Driver App Downloads</v>
       </c>
       <c r="B1" t="str">
         <v/>
@@ -7474,7 +7264,7 @@
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" t="str">
-        <v>Unit: Thousands of Accounts   |   Total registered buyer/member accounts, 2024. CarMax, Carvana &amp; eBay use B2C model — N/A.</v>
+        <v>Unit: Millions (cumulative)   |   Driver/transport app combined iOS + Android downloads, 2024. N/A where no dedicated app exists.</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -7564,7 +7354,7 @@
         <v>Company</v>
       </c>
       <c r="B5" t="str">
-        <v>Value (Thousands of Accounts)</v>
+        <v>Value (Millions (cumulative))</v>
       </c>
       <c r="C5" t="str">
         <v>Notes</v>
@@ -7593,10 +7383,10 @@
         <v>Copart</v>
       </c>
       <c r="B6">
-        <v>750</v>
+        <v>1</v>
       </c>
       <c r="C6" t="str">
-        <v>750 Thousands of Accounts</v>
+        <v>1 Millions (cumulative)</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -7622,10 +7412,10 @@
         <v>IAA</v>
       </c>
       <c r="B7">
-        <v>500</v>
+        <v>0.5</v>
       </c>
       <c r="C7" t="str">
-        <v>500 Thousands of Accounts</v>
+        <v>0.5 Millions (cumulative)</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -7651,10 +7441,10 @@
         <v>Manheim</v>
       </c>
       <c r="B8">
-        <v>70</v>
+        <v>0.3</v>
       </c>
       <c r="C8" t="str">
-        <v>70 Thousands of Accounts</v>
+        <v>0.3 Millions (cumulative)</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -7679,11 +7469,11 @@
       <c r="A9" t="str">
         <v>OpenLane</v>
       </c>
-      <c r="B9">
-        <v>85</v>
+      <c r="B9" t="str">
+        <v>N/A</v>
       </c>
       <c r="C9" t="str">
-        <v>85 Thousands of Accounts</v>
+        <v>Not applicable / not publicly reported</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -7709,10 +7499,10 @@
         <v>ACV</v>
       </c>
       <c r="B10">
-        <v>25</v>
+        <v>0.4</v>
       </c>
       <c r="C10" t="str">
-        <v>25 Thousands of Accounts</v>
+        <v>0.4 Millions (cumulative)</v>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -7737,11 +7527,11 @@
       <c r="A11" t="str">
         <v>CarMax</v>
       </c>
-      <c r="B11" t="str">
-        <v>N/A</v>
+      <c r="B11">
+        <v>0.8</v>
       </c>
       <c r="C11" t="str">
-        <v>Not applicable / not publicly reported</v>
+        <v>0.8 Millions (cumulative)</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -7766,11 +7556,11 @@
       <c r="A12" t="str">
         <v>Carvana</v>
       </c>
-      <c r="B12" t="str">
-        <v>N/A</v>
+      <c r="B12">
+        <v>1.2</v>
       </c>
       <c r="C12" t="str">
-        <v>Not applicable / not publicly reported</v>
+        <v>1.2 Millions (cumulative)</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -7909,28 +7699,28 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" t="str">
-        <v>Registered Global Buyers</v>
+        <v>Driver App Downloads</v>
       </c>
       <c r="B17">
-        <v>750</v>
+        <v>1</v>
       </c>
       <c r="C17">
-        <v>500</v>
+        <v>0.5</v>
       </c>
       <c r="D17">
-        <v>70</v>
-      </c>
-      <c r="E17">
-        <v>85</v>
+        <v>0.3</v>
+      </c>
+      <c r="E17" t="str">
+        <v>N/A</v>
       </c>
       <c r="F17">
-        <v>25</v>
-      </c>
-      <c r="G17" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H17" t="str">
-        <v>N/A</v>
+        <v>0.4</v>
+      </c>
+      <c r="G17">
+        <v>0.8</v>
+      </c>
+      <c r="H17">
+        <v>1.2</v>
       </c>
       <c r="I17" t="str">
         <v>N/A</v>
@@ -7941,28 +7731,28 @@
         <v>Unit</v>
       </c>
       <c r="B18" t="str">
-        <v>Thousands of Accounts</v>
+        <v>Millions (cumulative)</v>
       </c>
       <c r="C18" t="str">
-        <v>Thousands of Accounts</v>
+        <v>Millions (cumulative)</v>
       </c>
       <c r="D18" t="str">
-        <v>Thousands of Accounts</v>
+        <v>Millions (cumulative)</v>
       </c>
       <c r="E18" t="str">
-        <v>Thousands of Accounts</v>
+        <v>Millions (cumulative)</v>
       </c>
       <c r="F18" t="str">
-        <v>Thousands of Accounts</v>
+        <v>Millions (cumulative)</v>
       </c>
       <c r="G18" t="str">
-        <v>Thousands of Accounts</v>
+        <v>Millions (cumulative)</v>
       </c>
       <c r="H18" t="str">
-        <v>Thousands of Accounts</v>
+        <v>Millions (cumulative)</v>
       </c>
       <c r="I18" t="str">
-        <v>Thousands of Accounts</v>
+        <v>Millions (cumulative)</v>
       </c>
     </row>
   </sheetData>
@@ -7996,7 +7786,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" t="str">
-        <v>Buyer Countries</v>
+        <v>Registered Global Buyers</v>
       </c>
       <c r="B1" t="str">
         <v/>
@@ -8025,7 +7815,7 @@
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" t="str">
-        <v>Unit: Countries   |   Countries from which active buyers placed bids, 2024.</v>
+        <v>Unit: Thousands of Accounts   |   Total registered buyer/member accounts, 2024. CarMax, Carvana &amp; eBay use B2C model — N/A.</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -8115,7 +7905,7 @@
         <v>Company</v>
       </c>
       <c r="B5" t="str">
-        <v>Value (Countries)</v>
+        <v>Value (Thousands of Accounts)</v>
       </c>
       <c r="C5" t="str">
         <v>Notes</v>
@@ -8144,10 +7934,10 @@
         <v>Copart</v>
       </c>
       <c r="B6">
-        <v>170</v>
+        <v>750</v>
       </c>
       <c r="C6" t="str">
-        <v>170 Countries</v>
+        <v>750 Thousands of Accounts</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -8173,10 +7963,10 @@
         <v>IAA</v>
       </c>
       <c r="B7">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="C7" t="str">
-        <v>40 Countries</v>
+        <v>500 Thousands of Accounts</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -8202,10 +7992,10 @@
         <v>Manheim</v>
       </c>
       <c r="B8">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="C8" t="str">
-        <v>25 Countries</v>
+        <v>70 Thousands of Accounts</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -8231,10 +8021,10 @@
         <v>OpenLane</v>
       </c>
       <c r="B9">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="C9" t="str">
-        <v>20 Countries</v>
+        <v>85 Thousands of Accounts</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -8260,10 +8050,10 @@
         <v>ACV</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C10" t="str">
-        <v>3 Countries</v>
+        <v>25 Thousands of Accounts</v>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -8288,11 +8078,11 @@
       <c r="A11" t="str">
         <v>CarMax</v>
       </c>
-      <c r="B11">
-        <v>1</v>
+      <c r="B11" t="str">
+        <v>N/A</v>
       </c>
       <c r="C11" t="str">
-        <v>1 Countries</v>
+        <v>Not applicable / not publicly reported</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -8317,11 +8107,11 @@
       <c r="A12" t="str">
         <v>Carvana</v>
       </c>
-      <c r="B12">
-        <v>1</v>
+      <c r="B12" t="str">
+        <v>N/A</v>
       </c>
       <c r="C12" t="str">
-        <v>1 Countries</v>
+        <v>Not applicable / not publicly reported</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -8346,11 +8136,11 @@
       <c r="A13" t="str">
         <v>eBay Motors</v>
       </c>
-      <c r="B13">
-        <v>65</v>
+      <c r="B13" t="str">
+        <v>N/A</v>
       </c>
       <c r="C13" t="str">
-        <v>65 Countries</v>
+        <v>Not applicable / not publicly reported</v>
       </c>
       <c r="D13" t="str">
         <v/>
@@ -8460,31 +8250,31 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" t="str">
-        <v>Buyer Countries</v>
+        <v>Registered Global Buyers</v>
       </c>
       <c r="B17">
-        <v>170</v>
+        <v>750</v>
       </c>
       <c r="C17">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="D17">
+        <v>70</v>
+      </c>
+      <c r="E17">
+        <v>85</v>
+      </c>
+      <c r="F17">
         <v>25</v>
       </c>
-      <c r="E17">
-        <v>20</v>
-      </c>
-      <c r="F17">
-        <v>3</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-      <c r="H17">
-        <v>1</v>
-      </c>
-      <c r="I17">
-        <v>65</v>
+      <c r="G17" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H17" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I17" t="str">
+        <v>N/A</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -8492,28 +8282,28 @@
         <v>Unit</v>
       </c>
       <c r="B18" t="str">
-        <v>Countries</v>
+        <v>Thousands of Accounts</v>
       </c>
       <c r="C18" t="str">
-        <v>Countries</v>
+        <v>Thousands of Accounts</v>
       </c>
       <c r="D18" t="str">
-        <v>Countries</v>
+        <v>Thousands of Accounts</v>
       </c>
       <c r="E18" t="str">
-        <v>Countries</v>
+        <v>Thousands of Accounts</v>
       </c>
       <c r="F18" t="str">
-        <v>Countries</v>
+        <v>Thousands of Accounts</v>
       </c>
       <c r="G18" t="str">
-        <v>Countries</v>
+        <v>Thousands of Accounts</v>
       </c>
       <c r="H18" t="str">
-        <v>Countries</v>
+        <v>Thousands of Accounts</v>
       </c>
       <c r="I18" t="str">
-        <v>Countries</v>
+        <v>Thousands of Accounts</v>
       </c>
     </row>
   </sheetData>
@@ -8547,7 +8337,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" t="str">
-        <v>Monthly Social &amp; Web Mentions</v>
+        <v>Buyer Countries</v>
       </c>
       <c r="B1" t="str">
         <v/>
@@ -8576,7 +8366,7 @@
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" t="str">
-        <v>Unit: Thousands / Month   |   Estimated average monthly brand mentions across social platforms, news &amp; forums, 2024.</v>
+        <v>Unit: Countries   |   Countries from which active buyers placed bids, 2024.</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -8666,7 +8456,7 @@
         <v>Company</v>
       </c>
       <c r="B5" t="str">
-        <v>Value (Thousands / Month)</v>
+        <v>Value (Countries)</v>
       </c>
       <c r="C5" t="str">
         <v>Notes</v>
@@ -8695,10 +8485,10 @@
         <v>Copart</v>
       </c>
       <c r="B6">
-        <v>45</v>
+        <v>170</v>
       </c>
       <c r="C6" t="str">
-        <v>45 Thousands / Month</v>
+        <v>170 Countries</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -8724,10 +8514,10 @@
         <v>IAA</v>
       </c>
       <c r="B7">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C7" t="str">
-        <v>25 Thousands / Month</v>
+        <v>40 Countries</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -8753,10 +8543,10 @@
         <v>Manheim</v>
       </c>
       <c r="B8">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C8" t="str">
-        <v>35 Thousands / Month</v>
+        <v>25 Countries</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -8782,10 +8572,10 @@
         <v>OpenLane</v>
       </c>
       <c r="B9">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C9" t="str">
-        <v>8 Thousands / Month</v>
+        <v>20 Countries</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -8811,10 +8601,10 @@
         <v>ACV</v>
       </c>
       <c r="B10">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C10" t="str">
-        <v>12 Thousands / Month</v>
+        <v>3 Countries</v>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -8840,10 +8630,10 @@
         <v>CarMax</v>
       </c>
       <c r="B11">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="C11" t="str">
-        <v>180 Thousands / Month</v>
+        <v>1 Countries</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -8869,10 +8659,10 @@
         <v>Carvana</v>
       </c>
       <c r="B12">
-        <v>280</v>
+        <v>1</v>
       </c>
       <c r="C12" t="str">
-        <v>280 Thousands / Month</v>
+        <v>1 Countries</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -8898,10 +8688,10 @@
         <v>eBay Motors</v>
       </c>
       <c r="B13">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C13" t="str">
-        <v>55 Thousands / Month</v>
+        <v>65 Countries</v>
       </c>
       <c r="D13" t="str">
         <v/>
@@ -9011,31 +8801,31 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" t="str">
-        <v>Monthly Social &amp; Web Mentions</v>
+        <v>Buyer Countries</v>
       </c>
       <c r="B17">
-        <v>45</v>
+        <v>170</v>
       </c>
       <c r="C17">
+        <v>40</v>
+      </c>
+      <c r="D17">
         <v>25</v>
       </c>
-      <c r="D17">
-        <v>35</v>
-      </c>
       <c r="E17">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F17">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G17">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>280</v>
+        <v>1</v>
       </c>
       <c r="I17">
-        <v>55</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -9043,28 +8833,28 @@
         <v>Unit</v>
       </c>
       <c r="B18" t="str">
-        <v>Thousands / Month</v>
+        <v>Countries</v>
       </c>
       <c r="C18" t="str">
-        <v>Thousands / Month</v>
+        <v>Countries</v>
       </c>
       <c r="D18" t="str">
-        <v>Thousands / Month</v>
+        <v>Countries</v>
       </c>
       <c r="E18" t="str">
-        <v>Thousands / Month</v>
+        <v>Countries</v>
       </c>
       <c r="F18" t="str">
-        <v>Thousands / Month</v>
+        <v>Countries</v>
       </c>
       <c r="G18" t="str">
-        <v>Thousands / Month</v>
+        <v>Countries</v>
       </c>
       <c r="H18" t="str">
-        <v>Thousands / Month</v>
+        <v>Countries</v>
       </c>
       <c r="I18" t="str">
-        <v>Thousands / Month</v>
+        <v>Countries</v>
       </c>
     </row>
   </sheetData>
@@ -9098,7 +8888,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" t="str">
-        <v>B2B Auction Mentions (Excl. Retail)</v>
+        <v>Monthly Social &amp; Web Mentions</v>
       </c>
       <c r="B1" t="str">
         <v/>
@@ -9127,7 +8917,7 @@
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" t="str">
-        <v>Unit: Thousands / Month   |   Social mentions filtered to B2B/salvage-auction segment only, 2024. Retail platforms = N/A.</v>
+        <v>Unit: Thousands / Month   |   Estimated average monthly brand mentions across social platforms, news &amp; forums, 2024.</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -9390,11 +9180,11 @@
       <c r="A11" t="str">
         <v>CarMax</v>
       </c>
-      <c r="B11" t="str">
-        <v>N/A</v>
+      <c r="B11">
+        <v>180</v>
       </c>
       <c r="C11" t="str">
-        <v>Not applicable / not publicly reported</v>
+        <v>180 Thousands / Month</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -9419,11 +9209,11 @@
       <c r="A12" t="str">
         <v>Carvana</v>
       </c>
-      <c r="B12" t="str">
-        <v>N/A</v>
+      <c r="B12">
+        <v>280</v>
       </c>
       <c r="C12" t="str">
-        <v>Not applicable / not publicly reported</v>
+        <v>280 Thousands / Month</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -9562,7 +9352,7 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" t="str">
-        <v>B2B Auction Mentions (Excl. Retail)</v>
+        <v>Monthly Social &amp; Web Mentions</v>
       </c>
       <c r="B17">
         <v>45</v>
@@ -9579,11 +9369,11 @@
       <c r="F17">
         <v>12</v>
       </c>
-      <c r="G17" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H17" t="str">
-        <v>N/A</v>
+      <c r="G17">
+        <v>180</v>
+      </c>
+      <c r="H17">
+        <v>280</v>
       </c>
       <c r="I17">
         <v>55</v>
@@ -9649,7 +9439,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" t="str">
-        <v>YouTube Channel Subscribers</v>
+        <v>B2B Auction Mentions (Excl. Retail)</v>
       </c>
       <c r="B1" t="str">
         <v/>
@@ -9678,7 +9468,7 @@
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" t="str">
-        <v>Unit: Thousands of Subscribers   |   Official YouTube channel subscribers, 2024 estimate. B2B platforms have smaller but more targeted audiences.</v>
+        <v>Unit: Thousands / Month   |   Social mentions filtered to B2B/salvage-auction segment only, 2024. Retail platforms = N/A.</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -9768,7 +9558,7 @@
         <v>Company</v>
       </c>
       <c r="B5" t="str">
-        <v>Value (Thousands of Subscribers)</v>
+        <v>Value (Thousands / Month)</v>
       </c>
       <c r="C5" t="str">
         <v>Notes</v>
@@ -9797,10 +9587,10 @@
         <v>Copart</v>
       </c>
       <c r="B6">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="C6" t="str">
-        <v>90 Thousands of Subscribers</v>
+        <v>45 Thousands / Month</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -9826,10 +9616,10 @@
         <v>IAA</v>
       </c>
       <c r="B7">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C7" t="str">
-        <v>20 Thousands of Subscribers</v>
+        <v>25 Thousands / Month</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -9855,10 +9645,10 @@
         <v>Manheim</v>
       </c>
       <c r="B8">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C8" t="str">
-        <v>25 Thousands of Subscribers</v>
+        <v>35 Thousands / Month</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -9884,10 +9674,10 @@
         <v>OpenLane</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" t="str">
-        <v>7 Thousands of Subscribers</v>
+        <v>8 Thousands / Month</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -9913,10 +9703,10 @@
         <v>ACV</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C10" t="str">
-        <v>4 Thousands of Subscribers</v>
+        <v>12 Thousands / Month</v>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -9941,11 +9731,11 @@
       <c r="A11" t="str">
         <v>CarMax</v>
       </c>
-      <c r="B11">
-        <v>115</v>
+      <c r="B11" t="str">
+        <v>N/A</v>
       </c>
       <c r="C11" t="str">
-        <v>115 Thousands of Subscribers</v>
+        <v>Not applicable / not publicly reported</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -9970,11 +9760,11 @@
       <c r="A12" t="str">
         <v>Carvana</v>
       </c>
-      <c r="B12">
-        <v>60</v>
+      <c r="B12" t="str">
+        <v>N/A</v>
       </c>
       <c r="C12" t="str">
-        <v>60 Thousands of Subscribers</v>
+        <v>Not applicable / not publicly reported</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -10000,10 +9790,10 @@
         <v>eBay Motors</v>
       </c>
       <c r="B13">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C13" t="str">
-        <v>47 Thousands of Subscribers</v>
+        <v>55 Thousands / Month</v>
       </c>
       <c r="D13" t="str">
         <v/>
@@ -10113,31 +9903,31 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" t="str">
-        <v>YouTube Channel Subscribers</v>
+        <v>B2B Auction Mentions (Excl. Retail)</v>
       </c>
       <c r="B17">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="C17">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D17">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F17">
-        <v>4</v>
-      </c>
-      <c r="G17">
-        <v>115</v>
-      </c>
-      <c r="H17">
-        <v>60</v>
+        <v>12</v>
+      </c>
+      <c r="G17" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H17" t="str">
+        <v>N/A</v>
       </c>
       <c r="I17">
-        <v>47</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -10145,28 +9935,28 @@
         <v>Unit</v>
       </c>
       <c r="B18" t="str">
-        <v>Thousands of Subscribers</v>
+        <v>Thousands / Month</v>
       </c>
       <c r="C18" t="str">
-        <v>Thousands of Subscribers</v>
+        <v>Thousands / Month</v>
       </c>
       <c r="D18" t="str">
-        <v>Thousands of Subscribers</v>
+        <v>Thousands / Month</v>
       </c>
       <c r="E18" t="str">
-        <v>Thousands of Subscribers</v>
+        <v>Thousands / Month</v>
       </c>
       <c r="F18" t="str">
-        <v>Thousands of Subscribers</v>
+        <v>Thousands / Month</v>
       </c>
       <c r="G18" t="str">
-        <v>Thousands of Subscribers</v>
+        <v>Thousands / Month</v>
       </c>
       <c r="H18" t="str">
-        <v>Thousands of Subscribers</v>
+        <v>Thousands / Month</v>
       </c>
       <c r="I18" t="str">
-        <v>Thousands of Subscribers</v>
+        <v>Thousands / Month</v>
       </c>
     </row>
   </sheetData>
@@ -10200,7 +9990,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" t="str">
-        <v>Monthly YouTube Mentions</v>
+        <v>YouTube Channel Subscribers</v>
       </c>
       <c r="B1" t="str">
         <v/>
@@ -10229,7 +10019,7 @@
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" t="str">
-        <v>Unit: Thousands / Month   |   Est. monthly brand video mentions on YouTube (dedicated videos, reviews, creator references), 2024.</v>
+        <v>Unit: Thousands of Subscribers   |   Official YouTube channel subscribers, 2024 estimate. B2B platforms have smaller but more targeted audiences.</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -10319,7 +10109,7 @@
         <v>Company</v>
       </c>
       <c r="B5" t="str">
-        <v>Value (Thousands / Month)</v>
+        <v>Value (Thousands of Subscribers)</v>
       </c>
       <c r="C5" t="str">
         <v>Notes</v>
@@ -10348,10 +10138,10 @@
         <v>Copart</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="C6" t="str">
-        <v>8 Thousands / Month</v>
+        <v>90 Thousands of Subscribers</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -10377,10 +10167,10 @@
         <v>IAA</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C7" t="str">
-        <v>4 Thousands / Month</v>
+        <v>20 Thousands of Subscribers</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -10406,10 +10196,10 @@
         <v>Manheim</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C8" t="str">
-        <v>6 Thousands / Month</v>
+        <v>25 Thousands of Subscribers</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -10435,10 +10225,10 @@
         <v>OpenLane</v>
       </c>
       <c r="B9">
-        <v>1.5</v>
+        <v>7</v>
       </c>
       <c r="C9" t="str">
-        <v>1.5 Thousands / Month</v>
+        <v>7 Thousands of Subscribers</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -10464,10 +10254,10 @@
         <v>ACV</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10" t="str">
-        <v>2 Thousands / Month</v>
+        <v>4 Thousands of Subscribers</v>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -10493,10 +10283,10 @@
         <v>CarMax</v>
       </c>
       <c r="B11">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="C11" t="str">
-        <v>95 Thousands / Month</v>
+        <v>115 Thousands of Subscribers</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -10522,10 +10312,10 @@
         <v>Carvana</v>
       </c>
       <c r="B12">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="C12" t="str">
-        <v>120 Thousands / Month</v>
+        <v>60 Thousands of Subscribers</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -10551,10 +10341,10 @@
         <v>eBay Motors</v>
       </c>
       <c r="B13">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="C13" t="str">
-        <v>18 Thousands / Month</v>
+        <v>47 Thousands of Subscribers</v>
       </c>
       <c r="D13" t="str">
         <v/>
@@ -10664,31 +10454,31 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" t="str">
-        <v>Monthly YouTube Mentions</v>
+        <v>YouTube Channel Subscribers</v>
       </c>
       <c r="B17">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="C17">
+        <v>20</v>
+      </c>
+      <c r="D17">
+        <v>25</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+      <c r="F17">
         <v>4</v>
       </c>
-      <c r="D17">
-        <v>6</v>
-      </c>
-      <c r="E17">
-        <v>1.5</v>
-      </c>
-      <c r="F17">
-        <v>2</v>
-      </c>
       <c r="G17">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="H17">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="I17">
-        <v>18</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -10696,28 +10486,28 @@
         <v>Unit</v>
       </c>
       <c r="B18" t="str">
-        <v>Thousands / Month</v>
+        <v>Thousands of Subscribers</v>
       </c>
       <c r="C18" t="str">
-        <v>Thousands / Month</v>
+        <v>Thousands of Subscribers</v>
       </c>
       <c r="D18" t="str">
-        <v>Thousands / Month</v>
+        <v>Thousands of Subscribers</v>
       </c>
       <c r="E18" t="str">
-        <v>Thousands / Month</v>
+        <v>Thousands of Subscribers</v>
       </c>
       <c r="F18" t="str">
-        <v>Thousands / Month</v>
+        <v>Thousands of Subscribers</v>
       </c>
       <c r="G18" t="str">
-        <v>Thousands / Month</v>
+        <v>Thousands of Subscribers</v>
       </c>
       <c r="H18" t="str">
-        <v>Thousands / Month</v>
+        <v>Thousands of Subscribers</v>
       </c>
       <c r="I18" t="str">
-        <v>Thousands / Month</v>
+        <v>Thousands of Subscribers</v>
       </c>
     </row>
   </sheetData>
@@ -10751,6 +10541,557 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" t="str">
+        <v>Monthly YouTube Mentions</v>
+      </c>
+      <c r="B1" t="str">
+        <v/>
+      </c>
+      <c r="C1" t="str">
+        <v/>
+      </c>
+      <c r="D1" t="str">
+        <v/>
+      </c>
+      <c r="E1" t="str">
+        <v/>
+      </c>
+      <c r="F1" t="str">
+        <v/>
+      </c>
+      <c r="G1" t="str">
+        <v/>
+      </c>
+      <c r="H1" t="str">
+        <v/>
+      </c>
+      <c r="I1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" t="str">
+        <v>Unit: Thousands / Month   |   Est. monthly brand video mentions on YouTube (dedicated videos, reviews, creator references), 2024.</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1">
+      <c r="A3" t="str">
+        <v/>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" t="str">
+        <v>VERTICAL LAYOUT</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" t="str">
+        <v>Company</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Value (Thousands / Month)</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Notes</v>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" t="str">
+        <v>Copart</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6" t="str">
+        <v>8 Thousands / Month</v>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" t="str">
+        <v>IAA</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7" t="str">
+        <v>4 Thousands / Month</v>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" t="str">
+        <v>Manheim</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8" t="str">
+        <v>6 Thousands / Month</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" t="str">
+        <v>OpenLane</v>
+      </c>
+      <c r="B9">
+        <v>1.5</v>
+      </c>
+      <c r="C9" t="str">
+        <v>1.5 Thousands / Month</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" t="str">
+        <v>ACV</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10" t="str">
+        <v>2 Thousands / Month</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" t="str">
+        <v>CarMax</v>
+      </c>
+      <c r="B11">
+        <v>95</v>
+      </c>
+      <c r="C11" t="str">
+        <v>95 Thousands / Month</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" t="str">
+        <v>Carvana</v>
+      </c>
+      <c r="B12">
+        <v>120</v>
+      </c>
+      <c r="C12" t="str">
+        <v>120 Thousands / Month</v>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" t="str">
+        <v>eBay Motors</v>
+      </c>
+      <c r="B13">
+        <v>18</v>
+      </c>
+      <c r="C13" t="str">
+        <v>18 Thousands / Month</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="8" customHeight="1">
+      <c r="A14" t="str">
+        <v/>
+      </c>
+      <c r="B14" t="str">
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" t="str">
+        <v>HORIZONTAL LAYOUT</v>
+      </c>
+      <c r="B15" t="str">
+        <v/>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" t="str">
+        <v>Metric</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Copart</v>
+      </c>
+      <c r="C16" t="str">
+        <v>IAA</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Manheim</v>
+      </c>
+      <c r="E16" t="str">
+        <v>OpenLane</v>
+      </c>
+      <c r="F16" t="str">
+        <v>ACV</v>
+      </c>
+      <c r="G16" t="str">
+        <v>CarMax</v>
+      </c>
+      <c r="H16" t="str">
+        <v>Carvana</v>
+      </c>
+      <c r="I16" t="str">
+        <v>eBay Motors</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" t="str">
+        <v>Monthly YouTube Mentions</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>4</v>
+      </c>
+      <c r="D17">
+        <v>6</v>
+      </c>
+      <c r="E17">
+        <v>1.5</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17">
+        <v>95</v>
+      </c>
+      <c r="H17">
+        <v>120</v>
+      </c>
+      <c r="I17">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Thousands / Month</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Thousands / Month</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Thousands / Month</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Thousands / Month</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Thousands / Month</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Thousands / Month</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Thousands / Month</v>
+      </c>
+      <c r="I18" t="str">
+        <v>Thousands / Month</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="A15:I15"/>
+  </mergeCells>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I18"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I18"/>
+  <cols>
+    <col min="1" max="1" width="28.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="42.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" t="str">
         <v>Estimated Monthly SEM Spend</v>
       </c>
       <c r="B1" t="str">
@@ -11302,7 +11643,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" t="str">
-        <v>Market Capitalization</v>
+        <v>Annual Revenue</v>
       </c>
       <c r="B1" t="str">
         <v/>
@@ -11331,7 +11672,7 @@
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" t="str">
-        <v>Unit: USD Billions   |   Public market value, year-end 2024. Manheim (private) and eBay Motors (division) = N/A.</v>
+        <v>Unit: USD Billions   |   Most recent fiscal year (FY2024). CarMax &amp; Carvana include retail sales. eBay Motors is estimated.</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -11450,10 +11791,10 @@
         <v>Copart</v>
       </c>
       <c r="B6">
-        <v>54</v>
+        <v>4.19</v>
       </c>
       <c r="C6" t="str">
-        <v>54 USD Billions</v>
+        <v>4.19 USD Billions</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -11479,10 +11820,10 @@
         <v>IAA</v>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>4.06</v>
       </c>
       <c r="C7" t="str">
-        <v>8 USD Billions</v>
+        <v>4.06 USD Billions</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -11507,11 +11848,11 @@
       <c r="A8" t="str">
         <v>Manheim</v>
       </c>
-      <c r="B8" t="str">
-        <v>N/A</v>
+      <c r="B8">
+        <v>4.5</v>
       </c>
       <c r="C8" t="str">
-        <v>Not applicable / not publicly reported</v>
+        <v>4.5 USD Billions</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -11537,10 +11878,10 @@
         <v>OpenLane</v>
       </c>
       <c r="B9">
-        <v>1.1</v>
+        <v>0.91</v>
       </c>
       <c r="C9" t="str">
-        <v>1.1 USD Billions</v>
+        <v>0.91 USD Billions</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -11566,10 +11907,10 @@
         <v>ACV</v>
       </c>
       <c r="B10">
-        <v>1.4</v>
+        <v>0.63</v>
       </c>
       <c r="C10" t="str">
-        <v>1.4 USD Billions</v>
+        <v>0.63 USD Billions</v>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -11595,10 +11936,10 @@
         <v>CarMax</v>
       </c>
       <c r="B11">
-        <v>11</v>
+        <v>26.5</v>
       </c>
       <c r="C11" t="str">
-        <v>11 USD Billions</v>
+        <v>26.5 USD Billions</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -11624,10 +11965,10 @@
         <v>Carvana</v>
       </c>
       <c r="B12">
-        <v>49</v>
+        <v>13.7</v>
       </c>
       <c r="C12" t="str">
-        <v>49 USD Billions</v>
+        <v>13.7 USD Billions</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -11652,11 +11993,11 @@
       <c r="A13" t="str">
         <v>eBay Motors</v>
       </c>
-      <c r="B13" t="str">
-        <v>N/A</v>
+      <c r="B13">
+        <v>1.8</v>
       </c>
       <c r="C13" t="str">
-        <v>Not applicable / not publicly reported</v>
+        <v>1.8 USD Billions</v>
       </c>
       <c r="D13" t="str">
         <v/>
@@ -11766,31 +12107,31 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" t="str">
-        <v>Market Capitalization</v>
+        <v>Annual Revenue</v>
       </c>
       <c r="B17">
-        <v>54</v>
+        <v>4.19</v>
       </c>
       <c r="C17">
-        <v>8</v>
-      </c>
-      <c r="D17" t="str">
-        <v>N/A</v>
+        <v>4.06</v>
+      </c>
+      <c r="D17">
+        <v>4.5</v>
       </c>
       <c r="E17">
-        <v>1.1</v>
+        <v>0.91</v>
       </c>
       <c r="F17">
-        <v>1.4</v>
+        <v>0.63</v>
       </c>
       <c r="G17">
-        <v>11</v>
+        <v>26.5</v>
       </c>
       <c r="H17">
-        <v>49</v>
-      </c>
-      <c r="I17" t="str">
-        <v>N/A</v>
+        <v>13.7</v>
+      </c>
+      <c r="I17">
+        <v>1.8</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -11853,7 +12194,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" t="str">
-        <v>Capital Expenditure</v>
+        <v>Market Capitalization</v>
       </c>
       <c r="B1" t="str">
         <v/>
@@ -11882,7 +12223,7 @@
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" t="str">
-        <v>Unit: USD Billions   |   Annual capex FY2024. Manheim &amp; eBay Motors not separately reported. Copart reflects active land acquisition.</v>
+        <v>Unit: USD Billions   |   Public market value, year-end 2024. Manheim (private) and eBay Motors (division) = N/A.</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -12001,10 +12342,10 @@
         <v>Copart</v>
       </c>
       <c r="B6">
-        <v>1.1</v>
+        <v>54</v>
       </c>
       <c r="C6" t="str">
-        <v>1.1 USD Billions</v>
+        <v>54 USD Billions</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -12030,10 +12371,10 @@
         <v>IAA</v>
       </c>
       <c r="B7">
-        <v>0.22</v>
+        <v>8</v>
       </c>
       <c r="C7" t="str">
-        <v>0.22 USD Billions</v>
+        <v>8 USD Billions</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -12088,10 +12429,10 @@
         <v>OpenLane</v>
       </c>
       <c r="B9">
-        <v>0.065</v>
+        <v>1.1</v>
       </c>
       <c r="C9" t="str">
-        <v>0.065 USD Billions</v>
+        <v>1.1 USD Billions</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -12117,10 +12458,10 @@
         <v>ACV</v>
       </c>
       <c r="B10">
-        <v>0.04</v>
+        <v>1.4</v>
       </c>
       <c r="C10" t="str">
-        <v>0.04 USD Billions</v>
+        <v>1.4 USD Billions</v>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -12146,10 +12487,10 @@
         <v>CarMax</v>
       </c>
       <c r="B11">
-        <v>0.38</v>
+        <v>11</v>
       </c>
       <c r="C11" t="str">
-        <v>0.38 USD Billions</v>
+        <v>11 USD Billions</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -12175,10 +12516,10 @@
         <v>Carvana</v>
       </c>
       <c r="B12">
-        <v>0.35</v>
+        <v>49</v>
       </c>
       <c r="C12" t="str">
-        <v>0.35 USD Billions</v>
+        <v>49 USD Billions</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -12317,28 +12658,28 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" t="str">
-        <v>Capital Expenditure</v>
+        <v>Market Capitalization</v>
       </c>
       <c r="B17">
-        <v>1.1</v>
+        <v>54</v>
       </c>
       <c r="C17">
-        <v>0.22</v>
+        <v>8</v>
       </c>
       <c r="D17" t="str">
         <v>N/A</v>
       </c>
       <c r="E17">
-        <v>0.065</v>
+        <v>1.1</v>
       </c>
       <c r="F17">
-        <v>0.04</v>
+        <v>1.4</v>
       </c>
       <c r="G17">
-        <v>0.38</v>
+        <v>11</v>
       </c>
       <c r="H17">
-        <v>0.35</v>
+        <v>49</v>
       </c>
       <c r="I17" t="str">
         <v>N/A</v>
@@ -12404,7 +12745,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" t="str">
-        <v>Physical Locations</v>
+        <v>Capital Expenditure</v>
       </c>
       <c r="B1" t="str">
         <v/>
@@ -12433,7 +12774,7 @@
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" t="str">
-        <v>Unit: Number of Sites   |   Auction yards, storage lots &amp; reconditioning centres, 2024. ACV &amp; eBay are digital-only.</v>
+        <v>Unit: USD Billions   |   Annual capex FY2024. Manheim &amp; eBay Motors not separately reported. Copart reflects active land acquisition.</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -12523,7 +12864,7 @@
         <v>Company</v>
       </c>
       <c r="B5" t="str">
-        <v>Value (Number of Sites)</v>
+        <v>Value (USD Billions)</v>
       </c>
       <c r="C5" t="str">
         <v>Notes</v>
@@ -12552,10 +12893,10 @@
         <v>Copart</v>
       </c>
       <c r="B6">
-        <v>270</v>
+        <v>1.1</v>
       </c>
       <c r="C6" t="str">
-        <v>270 Number of Sites</v>
+        <v>1.1 USD Billions</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -12581,10 +12922,10 @@
         <v>IAA</v>
       </c>
       <c r="B7">
-        <v>200</v>
+        <v>0.22</v>
       </c>
       <c r="C7" t="str">
-        <v>200 Number of Sites</v>
+        <v>0.22 USD Billions</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -12609,11 +12950,11 @@
       <c r="A8" t="str">
         <v>Manheim</v>
       </c>
-      <c r="B8">
-        <v>75</v>
+      <c r="B8" t="str">
+        <v>N/A</v>
       </c>
       <c r="C8" t="str">
-        <v>75 Number of Sites</v>
+        <v>Not applicable / not publicly reported</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -12639,10 +12980,10 @@
         <v>OpenLane</v>
       </c>
       <c r="B9">
-        <v>30</v>
+        <v>0.065</v>
       </c>
       <c r="C9" t="str">
-        <v>30 Number of Sites</v>
+        <v>0.065 USD Billions</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -12668,10 +13009,10 @@
         <v>ACV</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="C10" t="str">
-        <v>0 Number of Sites</v>
+        <v>0.04 USD Billions</v>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -12697,10 +13038,10 @@
         <v>CarMax</v>
       </c>
       <c r="B11">
-        <v>246</v>
+        <v>0.38</v>
       </c>
       <c r="C11" t="str">
-        <v>246 Number of Sites</v>
+        <v>0.38 USD Billions</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -12726,10 +13067,10 @@
         <v>Carvana</v>
       </c>
       <c r="B12">
-        <v>36</v>
+        <v>0.35</v>
       </c>
       <c r="C12" t="str">
-        <v>36 Number of Sites</v>
+        <v>0.35 USD Billions</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -12754,11 +13095,11 @@
       <c r="A13" t="str">
         <v>eBay Motors</v>
       </c>
-      <c r="B13">
-        <v>0</v>
+      <c r="B13" t="str">
+        <v>N/A</v>
       </c>
       <c r="C13" t="str">
-        <v>0 Number of Sites</v>
+        <v>Not applicable / not publicly reported</v>
       </c>
       <c r="D13" t="str">
         <v/>
@@ -12868,31 +13209,31 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" t="str">
-        <v>Physical Locations</v>
+        <v>Capital Expenditure</v>
       </c>
       <c r="B17">
-        <v>270</v>
+        <v>1.1</v>
       </c>
       <c r="C17">
-        <v>200</v>
-      </c>
-      <c r="D17">
-        <v>75</v>
+        <v>0.22</v>
+      </c>
+      <c r="D17" t="str">
+        <v>N/A</v>
       </c>
       <c r="E17">
-        <v>30</v>
+        <v>0.065</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="G17">
-        <v>246</v>
+        <v>0.38</v>
       </c>
       <c r="H17">
-        <v>36</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
+        <v>0.35</v>
+      </c>
+      <c r="I17" t="str">
+        <v>N/A</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -12900,28 +13241,28 @@
         <v>Unit</v>
       </c>
       <c r="B18" t="str">
-        <v>Number of Sites</v>
+        <v>USD Billions</v>
       </c>
       <c r="C18" t="str">
-        <v>Number of Sites</v>
+        <v>USD Billions</v>
       </c>
       <c r="D18" t="str">
-        <v>Number of Sites</v>
+        <v>USD Billions</v>
       </c>
       <c r="E18" t="str">
-        <v>Number of Sites</v>
+        <v>USD Billions</v>
       </c>
       <c r="F18" t="str">
-        <v>Number of Sites</v>
+        <v>USD Billions</v>
       </c>
       <c r="G18" t="str">
-        <v>Number of Sites</v>
+        <v>USD Billions</v>
       </c>
       <c r="H18" t="str">
-        <v>Number of Sites</v>
+        <v>USD Billions</v>
       </c>
       <c r="I18" t="str">
-        <v>Number of Sites</v>
+        <v>USD Billions</v>
       </c>
     </row>
   </sheetData>
@@ -12955,7 +13296,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" t="str">
-        <v>Land Footprint</v>
+        <v>Physical Locations</v>
       </c>
       <c r="B1" t="str">
         <v/>
@@ -12984,7 +13325,7 @@
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" t="str">
-        <v>Unit: Thousands of Acres   |   Total owned &amp; operated acreage, 2024. Digital-first platforms show near-zero.</v>
+        <v>Unit: Number of Sites   |   Auction yards, storage lots &amp; reconditioning centres, 2024. ACV &amp; eBay are digital-only.</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -13074,7 +13415,7 @@
         <v>Company</v>
       </c>
       <c r="B5" t="str">
-        <v>Value (Thousands of Acres)</v>
+        <v>Value (Number of Sites)</v>
       </c>
       <c r="C5" t="str">
         <v>Notes</v>
@@ -13103,10 +13444,10 @@
         <v>Copart</v>
       </c>
       <c r="B6">
-        <v>120</v>
+        <v>270</v>
       </c>
       <c r="C6" t="str">
-        <v>120 Thousands of Acres</v>
+        <v>270 Number of Sites</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -13132,10 +13473,10 @@
         <v>IAA</v>
       </c>
       <c r="B7">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="C7" t="str">
-        <v>30 Thousands of Acres</v>
+        <v>200 Number of Sites</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -13161,10 +13502,10 @@
         <v>Manheim</v>
       </c>
       <c r="B8">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="C8" t="str">
-        <v>14 Thousands of Acres</v>
+        <v>75 Number of Sites</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -13190,10 +13531,10 @@
         <v>OpenLane</v>
       </c>
       <c r="B9">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C9" t="str">
-        <v>4 Thousands of Acres</v>
+        <v>30 Number of Sites</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -13222,7 +13563,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="str">
-        <v>0 Thousands of Acres</v>
+        <v>0 Number of Sites</v>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -13248,10 +13589,10 @@
         <v>CarMax</v>
       </c>
       <c r="B11">
-        <v>5</v>
+        <v>246</v>
       </c>
       <c r="C11" t="str">
-        <v>5 Thousands of Acres</v>
+        <v>246 Number of Sites</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -13277,10 +13618,10 @@
         <v>Carvana</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="C12" t="str">
-        <v>2 Thousands of Acres</v>
+        <v>36 Number of Sites</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -13309,7 +13650,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="str">
-        <v>0 Thousands of Acres</v>
+        <v>0 Number of Sites</v>
       </c>
       <c r="D13" t="str">
         <v/>
@@ -13419,28 +13760,28 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" t="str">
-        <v>Land Footprint</v>
+        <v>Physical Locations</v>
       </c>
       <c r="B17">
-        <v>120</v>
+        <v>270</v>
       </c>
       <c r="C17">
+        <v>200</v>
+      </c>
+      <c r="D17">
+        <v>75</v>
+      </c>
+      <c r="E17">
         <v>30</v>
-      </c>
-      <c r="D17">
-        <v>14</v>
-      </c>
-      <c r="E17">
-        <v>4</v>
       </c>
       <c r="F17">
         <v>0</v>
       </c>
       <c r="G17">
-        <v>5</v>
+        <v>246</v>
       </c>
       <c r="H17">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -13451,28 +13792,28 @@
         <v>Unit</v>
       </c>
       <c r="B18" t="str">
-        <v>Thousands of Acres</v>
+        <v>Number of Sites</v>
       </c>
       <c r="C18" t="str">
-        <v>Thousands of Acres</v>
+        <v>Number of Sites</v>
       </c>
       <c r="D18" t="str">
-        <v>Thousands of Acres</v>
+        <v>Number of Sites</v>
       </c>
       <c r="E18" t="str">
-        <v>Thousands of Acres</v>
+        <v>Number of Sites</v>
       </c>
       <c r="F18" t="str">
-        <v>Thousands of Acres</v>
+        <v>Number of Sites</v>
       </c>
       <c r="G18" t="str">
-        <v>Thousands of Acres</v>
+        <v>Number of Sites</v>
       </c>
       <c r="H18" t="str">
-        <v>Thousands of Acres</v>
+        <v>Number of Sites</v>
       </c>
       <c r="I18" t="str">
-        <v>Thousands of Acres</v>
+        <v>Number of Sites</v>
       </c>
     </row>
   </sheetData>
@@ -13506,7 +13847,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" t="str">
-        <v>Countries of Operation</v>
+        <v>Land Footprint</v>
       </c>
       <c r="B1" t="str">
         <v/>
@@ -13535,7 +13876,7 @@
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" t="str">
-        <v>Unit: Countries   |   Countries with active physical or digital operations, 2024.</v>
+        <v>Unit: Thousands of Acres   |   Total owned &amp; operated acreage, 2024. Digital-first platforms show near-zero.</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -13625,7 +13966,7 @@
         <v>Company</v>
       </c>
       <c r="B5" t="str">
-        <v>Value (Countries)</v>
+        <v>Value (Thousands of Acres)</v>
       </c>
       <c r="C5" t="str">
         <v>Notes</v>
@@ -13654,10 +13995,10 @@
         <v>Copart</v>
       </c>
       <c r="B6">
-        <v>11</v>
+        <v>120</v>
       </c>
       <c r="C6" t="str">
-        <v>11 Countries</v>
+        <v>120 Thousands of Acres</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -13683,10 +14024,10 @@
         <v>IAA</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="C7" t="str">
-        <v>2 Countries</v>
+        <v>30 Thousands of Acres</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -13712,10 +14053,10 @@
         <v>Manheim</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C8" t="str">
-        <v>4 Countries</v>
+        <v>14 Thousands of Acres</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -13741,10 +14082,10 @@
         <v>OpenLane</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="str">
-        <v>3 Countries</v>
+        <v>4 Thousands of Acres</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -13770,10 +14111,10 @@
         <v>ACV</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C10" t="str">
-        <v>2 Countries</v>
+        <v>0 Thousands of Acres</v>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -13799,10 +14140,10 @@
         <v>CarMax</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C11" t="str">
-        <v>1 Countries</v>
+        <v>5 Thousands of Acres</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -13828,10 +14169,10 @@
         <v>Carvana</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="str">
-        <v>1 Countries</v>
+        <v>2 Thousands of Acres</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -13857,10 +14198,10 @@
         <v>eBay Motors</v>
       </c>
       <c r="B13">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C13" t="str">
-        <v>15 Countries</v>
+        <v>0 Thousands of Acres</v>
       </c>
       <c r="D13" t="str">
         <v/>
@@ -13970,31 +14311,31 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" t="str">
-        <v>Countries of Operation</v>
+        <v>Land Footprint</v>
       </c>
       <c r="B17">
-        <v>11</v>
+        <v>120</v>
       </c>
       <c r="C17">
+        <v>30</v>
+      </c>
+      <c r="D17">
+        <v>14</v>
+      </c>
+      <c r="E17">
+        <v>4</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+      <c r="H17">
         <v>2</v>
       </c>
-      <c r="D17">
-        <v>4</v>
-      </c>
-      <c r="E17">
-        <v>3</v>
-      </c>
-      <c r="F17">
-        <v>2</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-      <c r="H17">
-        <v>1</v>
-      </c>
       <c r="I17">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -14002,28 +14343,28 @@
         <v>Unit</v>
       </c>
       <c r="B18" t="str">
-        <v>Countries</v>
+        <v>Thousands of Acres</v>
       </c>
       <c r="C18" t="str">
-        <v>Countries</v>
+        <v>Thousands of Acres</v>
       </c>
       <c r="D18" t="str">
-        <v>Countries</v>
+        <v>Thousands of Acres</v>
       </c>
       <c r="E18" t="str">
-        <v>Countries</v>
+        <v>Thousands of Acres</v>
       </c>
       <c r="F18" t="str">
-        <v>Countries</v>
+        <v>Thousands of Acres</v>
       </c>
       <c r="G18" t="str">
-        <v>Countries</v>
+        <v>Thousands of Acres</v>
       </c>
       <c r="H18" t="str">
-        <v>Countries</v>
+        <v>Thousands of Acres</v>
       </c>
       <c r="I18" t="str">
-        <v>Countries</v>
+        <v>Thousands of Acres</v>
       </c>
     </row>
   </sheetData>
@@ -14057,7 +14398,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" t="str">
-        <v>Vehicles Auctioned / Available</v>
+        <v>Countries of Operation</v>
       </c>
       <c r="B1" t="str">
         <v/>
@@ -14086,7 +14427,7 @@
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" t="str">
-        <v>Unit: Millions / Year   |   Vehicles consigned / listed to auction per year, FY2024.</v>
+        <v>Unit: Countries   |   Countries with active physical or digital operations, 2024.</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -14176,7 +14517,7 @@
         <v>Company</v>
       </c>
       <c r="B5" t="str">
-        <v>Value (Millions / Year)</v>
+        <v>Value (Countries)</v>
       </c>
       <c r="C5" t="str">
         <v>Notes</v>
@@ -14205,10 +14546,10 @@
         <v>Copart</v>
       </c>
       <c r="B6">
-        <v>3.6</v>
+        <v>11</v>
       </c>
       <c r="C6" t="str">
-        <v>3.6 Millions / Year</v>
+        <v>11 Countries</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -14234,10 +14575,10 @@
         <v>IAA</v>
       </c>
       <c r="B7">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="C7" t="str">
-        <v>2.4 Millions / Year</v>
+        <v>2 Countries</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -14263,10 +14604,10 @@
         <v>Manheim</v>
       </c>
       <c r="B8">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C8" t="str">
-        <v>10 Millions / Year</v>
+        <v>4 Countries</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -14292,10 +14633,10 @@
         <v>OpenLane</v>
       </c>
       <c r="B9">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="C9" t="str">
-        <v>1.6 Millions / Year</v>
+        <v>3 Countries</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -14321,10 +14662,10 @@
         <v>ACV</v>
       </c>
       <c r="B10">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="C10" t="str">
-        <v>0.6 Millions / Year</v>
+        <v>2 Countries</v>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -14350,10 +14691,10 @@
         <v>CarMax</v>
       </c>
       <c r="B11">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="C11" t="str">
-        <v>0.95 Millions / Year</v>
+        <v>1 Countries</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -14379,10 +14720,10 @@
         <v>Carvana</v>
       </c>
       <c r="B12">
-        <v>0.45</v>
+        <v>1</v>
       </c>
       <c r="C12" t="str">
-        <v>0.45 Millions / Year</v>
+        <v>1 Countries</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -14408,10 +14749,10 @@
         <v>eBay Motors</v>
       </c>
       <c r="B13">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C13" t="str">
-        <v>3 Millions / Year</v>
+        <v>15 Countries</v>
       </c>
       <c r="D13" t="str">
         <v/>
@@ -14521,31 +14862,31 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" t="str">
-        <v>Vehicles Auctioned / Available</v>
+        <v>Countries of Operation</v>
       </c>
       <c r="B17">
-        <v>3.6</v>
+        <v>11</v>
       </c>
       <c r="C17">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="D17">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E17">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="F17">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="G17">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>0.45</v>
+        <v>1</v>
       </c>
       <c r="I17">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -14553,28 +14894,28 @@
         <v>Unit</v>
       </c>
       <c r="B18" t="str">
-        <v>Millions / Year</v>
+        <v>Countries</v>
       </c>
       <c r="C18" t="str">
-        <v>Millions / Year</v>
+        <v>Countries</v>
       </c>
       <c r="D18" t="str">
-        <v>Millions / Year</v>
+        <v>Countries</v>
       </c>
       <c r="E18" t="str">
-        <v>Millions / Year</v>
+        <v>Countries</v>
       </c>
       <c r="F18" t="str">
-        <v>Millions / Year</v>
+        <v>Countries</v>
       </c>
       <c r="G18" t="str">
-        <v>Millions / Year</v>
+        <v>Countries</v>
       </c>
       <c r="H18" t="str">
-        <v>Millions / Year</v>
+        <v>Countries</v>
       </c>
       <c r="I18" t="str">
-        <v>Millions / Year</v>
+        <v>Countries</v>
       </c>
     </row>
   </sheetData>
@@ -14608,7 +14949,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" t="str">
-        <v>Vehicles Sold Annually</v>
+        <v>Vehicles Auctioned / Available</v>
       </c>
       <c r="B1" t="str">
         <v/>
@@ -14637,7 +14978,7 @@
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" t="str">
-        <v>Unit: Millions / Year   |   Vehicles actually sold at auction / retail, FY2024. Reflects sell-through rate.</v>
+        <v>Unit: Millions / Year   |   Vehicles consigned / listed to auction per year, FY2024.</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -14756,10 +15097,10 @@
         <v>Copart</v>
       </c>
       <c r="B6">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="C6" t="str">
-        <v>3.5 Millions / Year</v>
+        <v>3.6 Millions / Year</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -14785,10 +15126,10 @@
         <v>IAA</v>
       </c>
       <c r="B7">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="C7" t="str">
-        <v>2.2 Millions / Year</v>
+        <v>2.4 Millions / Year</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -14814,10 +15155,10 @@
         <v>Manheim</v>
       </c>
       <c r="B8">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="C8" t="str">
-        <v>8.5 Millions / Year</v>
+        <v>10 Millions / Year</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -14843,10 +15184,10 @@
         <v>OpenLane</v>
       </c>
       <c r="B9">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="C9" t="str">
-        <v>1.3 Millions / Year</v>
+        <v>1.6 Millions / Year</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -14872,10 +15213,10 @@
         <v>ACV</v>
       </c>
       <c r="B10">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="C10" t="str">
-        <v>0.55 Millions / Year</v>
+        <v>0.6 Millions / Year</v>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -14901,10 +15242,10 @@
         <v>CarMax</v>
       </c>
       <c r="B11">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="C11" t="str">
-        <v>0.9 Millions / Year</v>
+        <v>0.95 Millions / Year</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -14930,10 +15271,10 @@
         <v>Carvana</v>
       </c>
       <c r="B12">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="C12" t="str">
-        <v>0.42 Millions / Year</v>
+        <v>0.45 Millions / Year</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -14959,10 +15300,10 @@
         <v>eBay Motors</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="str">
-        <v>2 Millions / Year</v>
+        <v>3 Millions / Year</v>
       </c>
       <c r="D13" t="str">
         <v/>
@@ -15072,31 +15413,31 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" t="str">
-        <v>Vehicles Sold Annually</v>
+        <v>Vehicles Auctioned / Available</v>
       </c>
       <c r="B17">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="C17">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="D17">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="E17">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="F17">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="G17">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="H17">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="I17">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
